--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_39.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2741446.245701354</v>
+        <v>2742534.366176158</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>287242.3594286051</v>
+        <v>287242.3594286052</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287242.3594286051</v>
+        <v>287242.3594286052</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.347322035759451</v>
+        <v>3.347322035758897</v>
       </c>
       <c r="H2" t="n">
         <v>3.81023156784903</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.798687867827562</v>
       </c>
       <c r="S2" t="n">
-        <v>87.3028355696476</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>271.5879010453488</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>102.116498119979</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>374</v>
       </c>
       <c r="U3" t="n">
         <v>0.1959257979225981</v>
@@ -912,7 +912,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
         <v>184.8805867536895</v>
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>334.8709689755848</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>27.77864455057905</v>
       </c>
     </row>
     <row r="7">
@@ -1146,7 +1146,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T8" t="n">
         <v>184.8805867536895</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>185.4750894878712</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>78.54339244579138</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1386,7 +1386,7 @@
         <v>73.31166372865306</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.1143290738567457</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.2584265244209</v>
+        <v>142.1440974505641</v>
       </c>
       <c r="T11" t="n">
         <v>260.3930993165036</v>
@@ -1447,13 +1447,13 @@
         <v>64.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>41.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>27.93768689770263</v>
+        <v>230.9884566674124</v>
       </c>
       <c r="E12" t="n">
-        <v>22.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>19.63624233787687</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>382.6482274394477</v>
+        <v>179.5974576697378</v>
       </c>
       <c r="S12" t="n">
         <v>132.3008395872528</v>
@@ -1501,7 +1501,7 @@
         <v>82.2626425760044</v>
       </c>
       <c r="U12" t="n">
-        <v>80.1598408922622</v>
+        <v>400.1598408922622</v>
       </c>
       <c r="V12" t="n">
         <v>414.5106671915202</v>
@@ -1513,7 +1513,7 @@
         <v>99.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>79.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1623,7 +1623,7 @@
         <v>73.31166372865306</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1143290738567457</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.1143290738568794</v>
       </c>
       <c r="S14" t="n">
         <v>142.1440974505641</v>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>267.6073264160366</v>
       </c>
       <c r="C15" t="n">
         <v>41.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>22.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>222.6870121075869</v>
+        <v>19.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>4.971649082574515</v>
@@ -1744,13 +1744,13 @@
         <v>94.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>112.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>99.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>79.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1860,7 +1860,7 @@
         <v>73.31166372865304</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1143290738567598</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U17" t="n">
-        <v>329.1064824782589</v>
+        <v>329.2208115521158</v>
       </c>
       <c r="V17" t="n">
         <v>309.8510241668239</v>
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>267.6073264160368</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>41.09991244551929</v>
+        <v>169.0914925964479</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>22.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>19.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>4.971649082574513</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R18" t="n">
         <v>179.5974576697378</v>
@@ -1984,10 +1984,10 @@
         <v>112.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>99.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>79.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>267.6073264160366</v>
       </c>
       <c r="C21" t="n">
-        <v>41.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>27.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>22.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>19.63624233787687</v>
@@ -2212,13 +2212,13 @@
         <v>82.2626425760044</v>
       </c>
       <c r="U21" t="n">
-        <v>283.2106106619721</v>
+        <v>80.1598408922622</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>94.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>112.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>99.86273944538755</v>
@@ -2331,10 +2331,10 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H23" t="n">
-        <v>73.42599280250981</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.1143290738567457</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U23" t="n">
-        <v>329.1064824782589</v>
+        <v>329.106482478259</v>
       </c>
       <c r="V23" t="n">
         <v>309.8510241668239</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>267.6073264160366</v>
+        <v>64.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>244.1506822152293</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -2404,13 +2404,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>19.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>4.971649082574513</v>
+        <v>4.971649082574515</v>
       </c>
       <c r="H24" t="n">
-        <v>4.751917375100376</v>
+        <v>4.75191737510039</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2446,10 +2446,10 @@
         <v>132.3008395872528</v>
       </c>
       <c r="T24" t="n">
-        <v>82.26264257600438</v>
+        <v>82.2626425760044</v>
       </c>
       <c r="U24" t="n">
-        <v>80.15984089226222</v>
+        <v>80.1598408922622</v>
       </c>
       <c r="V24" t="n">
         <v>94.51066719152016</v>
@@ -2501,19 +2501,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>7.836513403680812</v>
+        <v>7.836513403680783</v>
       </c>
       <c r="M25" t="n">
-        <v>99.71766058287777</v>
+        <v>99.71766058287778</v>
       </c>
       <c r="N25" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O25" t="n">
-        <v>229.4515312921297</v>
+        <v>229.4515312921296</v>
       </c>
       <c r="P25" t="n">
-        <v>289.5867825741792</v>
+        <v>289.5867825741791</v>
       </c>
       <c r="Q25" t="n">
         <v>351.932266425598</v>
@@ -2522,7 +2522,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S25" t="n">
-        <v>31.15431576842921</v>
+        <v>31.15431576842923</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H26" t="n">
-        <v>73.42599280250981</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.1143290738568794</v>
       </c>
       <c r="S26" t="n">
         <v>142.1440974505641</v>
@@ -2607,7 +2607,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U26" t="n">
-        <v>329.1064824782589</v>
+        <v>329.106482478259</v>
       </c>
       <c r="V26" t="n">
         <v>309.8510241668239</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
         <v>41.09991244551929</v>
@@ -2638,16 +2638,16 @@
         <v>27.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>22.67209722191262</v>
+        <v>150.6636773728413</v>
       </c>
       <c r="F27" t="n">
-        <v>19.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>324.9716490825745</v>
+        <v>4.971649082574515</v>
       </c>
       <c r="H27" t="n">
-        <v>324.7519173751004</v>
+        <v>4.75191737510039</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2674,22 +2674,22 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R27" t="n">
-        <v>499.5974576697378</v>
+        <v>179.5974576697378</v>
       </c>
       <c r="S27" t="n">
         <v>132.3008395872528</v>
       </c>
       <c r="T27" t="n">
-        <v>82.26264257600438</v>
+        <v>82.2626425760044</v>
       </c>
       <c r="U27" t="n">
-        <v>80.15984089226222</v>
+        <v>80.1598408922622</v>
       </c>
       <c r="V27" t="n">
-        <v>297.5614369612301</v>
+        <v>94.51066719152016</v>
       </c>
       <c r="W27" t="n">
         <v>112.3731429098285</v>
@@ -2698,7 +2698,7 @@
         <v>99.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>79.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2738,19 +2738,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>7.836513403680812</v>
+        <v>7.836513403680783</v>
       </c>
       <c r="M28" t="n">
-        <v>99.71766058287777</v>
+        <v>99.71766058287778</v>
       </c>
       <c r="N28" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O28" t="n">
-        <v>229.4515312921297</v>
+        <v>229.4515312921296</v>
       </c>
       <c r="P28" t="n">
-        <v>289.5867825741792</v>
+        <v>289.5867825741791</v>
       </c>
       <c r="Q28" t="n">
         <v>351.932266425598</v>
@@ -2759,7 +2759,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S28" t="n">
-        <v>31.15431576842921</v>
+        <v>31.15431576842923</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H29" t="n">
-        <v>73.31166372865304</v>
+        <v>73.42599280250981</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1143290738568794</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.1440974505641</v>
@@ -2872,22 +2872,22 @@
         <v>41.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>35.0346886474441</v>
+        <v>22.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>19.63624233787687</v>
       </c>
       <c r="G30" t="n">
         <v>4.971649082574513</v>
       </c>
       <c r="H30" t="n">
-        <v>324.7519173751004</v>
+        <v>4.751917375100376</v>
       </c>
       <c r="I30" t="n">
-        <v>190.6881783441787</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.5974576697378</v>
+        <v>382.6482274394477</v>
       </c>
       <c r="S30" t="n">
         <v>132.3008395872528</v>
@@ -2926,13 +2926,13 @@
         <v>80.15984089226222</v>
       </c>
       <c r="V30" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>112.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>99.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>79.39139276613435</v>
@@ -3042,7 +3042,7 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H32" t="n">
-        <v>73.31166372865306</v>
+        <v>73.31166372865304</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U32" t="n">
-        <v>329.106482478259</v>
+        <v>329.1064824782589</v>
       </c>
       <c r="V32" t="n">
         <v>309.8510241668239</v>
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>267.6073264160366</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>244.1506822152292</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E33" t="n">
         <v>22.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>19.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>4.971649082574515</v>
+        <v>4.971649082574513</v>
       </c>
       <c r="H33" t="n">
-        <v>4.75191737510039</v>
+        <v>4.751917375100376</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3157,16 +3157,16 @@
         <v>132.3008395872528</v>
       </c>
       <c r="T33" t="n">
-        <v>82.2626425760044</v>
+        <v>82.26264257600438</v>
       </c>
       <c r="U33" t="n">
-        <v>80.1598408922622</v>
+        <v>80.15984089226222</v>
       </c>
       <c r="V33" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>112.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>99.86273944538755</v>
@@ -3212,19 +3212,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>7.836513403680783</v>
+        <v>7.836513403680812</v>
       </c>
       <c r="M34" t="n">
-        <v>99.71766058287778</v>
+        <v>99.71766058287777</v>
       </c>
       <c r="N34" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O34" t="n">
-        <v>229.4515312921296</v>
+        <v>229.4515312921297</v>
       </c>
       <c r="P34" t="n">
-        <v>289.5867825741791</v>
+        <v>289.5867825741792</v>
       </c>
       <c r="Q34" t="n">
         <v>351.932266425598</v>
@@ -3233,7 +3233,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S34" t="n">
-        <v>31.15431576842923</v>
+        <v>31.15431576842921</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>21.31166372865304</v>
       </c>
       <c r="I35" t="n">
-        <v>6.285529073856511</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.285529073856519</v>
       </c>
       <c r="S35" t="n">
         <v>90.1440974505641</v>
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>12.55655664632661</v>
       </c>
       <c r="C36" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>127.5974576697378</v>
       </c>
       <c r="S36" t="n">
-        <v>80.30083958725282</v>
+        <v>380.0286633376635</v>
       </c>
       <c r="T36" t="n">
         <v>30.26264257600438</v>
@@ -3403,13 +3403,13 @@
         <v>42.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>306.7107507798543</v>
+        <v>60.37314290982852</v>
       </c>
       <c r="X36" t="n">
         <v>47.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>27.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3516,10 +3516,10 @@
         <v>30.32219640761923</v>
       </c>
       <c r="H38" t="n">
-        <v>21.31166372865306</v>
+        <v>21.31166372865304</v>
       </c>
       <c r="I38" t="n">
-        <v>6.285529073856497</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>6.285529073856519</v>
       </c>
       <c r="S38" t="n">
-        <v>90.14409745056412</v>
+        <v>90.1440974505641</v>
       </c>
       <c r="T38" t="n">
         <v>208.3930993165036</v>
       </c>
       <c r="U38" t="n">
-        <v>277.106482478259</v>
+        <v>277.1064824782589</v>
       </c>
       <c r="V38" t="n">
         <v>257.8510241668239</v>
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>89.66965627981645</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>235.4375203155454</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>190.6881783441787</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,10 +3631,10 @@
         <v>80.30083958725282</v>
       </c>
       <c r="T39" t="n">
-        <v>30.2626425760044</v>
+        <v>402.2626425760044</v>
       </c>
       <c r="U39" t="n">
-        <v>28.1598408922622</v>
+        <v>400.1598408922622</v>
       </c>
       <c r="V39" t="n">
         <v>42.51066719152016</v>
@@ -3643,10 +3643,10 @@
         <v>60.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>47.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>27.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3689,16 +3689,16 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>47.71766058287778</v>
+        <v>47.71766058287777</v>
       </c>
       <c r="N40" t="n">
-        <v>100.6706326487341</v>
+        <v>100.670632648734</v>
       </c>
       <c r="O40" t="n">
-        <v>177.4515312921296</v>
+        <v>177.4515312921297</v>
       </c>
       <c r="P40" t="n">
-        <v>237.5867825741791</v>
+        <v>237.5867825741792</v>
       </c>
       <c r="Q40" t="n">
         <v>299.932266425598</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>34.13947147930534</v>
+        <v>161.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>129.4745782429939</v>
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>142.1440974505641</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>260.3930993165036</v>
       </c>
       <c r="U41" t="n">
         <v>329.1064824782589</v>
@@ -3798,10 +3798,10 @@
         <v>309.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>318.3734759809475</v>
+        <v>60.25827119827861</v>
       </c>
       <c r="X41" t="n">
-        <v>272.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3820,19 +3820,19 @@
         <v>41.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>22.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>19.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>4.971649082574513</v>
+        <v>324.9716490825745</v>
       </c>
       <c r="H42" t="n">
-        <v>127.1199323299596</v>
+        <v>52.06074271117838</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R42" t="n">
         <v>179.5974576697378</v>
@@ -3871,7 +3871,7 @@
         <v>82.26264257600438</v>
       </c>
       <c r="U42" t="n">
-        <v>400.1598408922622</v>
+        <v>80.15984089226222</v>
       </c>
       <c r="V42" t="n">
         <v>94.51066719152016</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>144.9579691869619</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3981,16 +3981,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>84.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>84.88962870801186</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>142.1440974505641</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>260.3930993165036</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>329.106482478259</v>
@@ -4041,7 +4041,7 @@
         <v>272.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>176.3027871462343</v>
+        <v>191.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4069,7 +4069,7 @@
         <v>4.971649082574515</v>
       </c>
       <c r="H45" t="n">
-        <v>127.1199323299598</v>
+        <v>127.1199323299596</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4108,16 +4108,16 @@
         <v>82.2626425760044</v>
       </c>
       <c r="U45" t="n">
-        <v>80.1598408922622</v>
+        <v>400.1598408922622</v>
       </c>
       <c r="V45" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>432.3731429098285</v>
+        <v>112.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>99.86273944538755</v>
       </c>
       <c r="Y45" t="n">
         <v>79.39139276613435</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.9141473750835</v>
+        <v>106.914147375083</v>
       </c>
       <c r="C2" t="n">
-        <v>56.93982591751391</v>
+        <v>56.93982591751335</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426109999</v>
+        <v>46.49623426109942</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183873</v>
+        <v>42.08887102183817</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485706</v>
+        <v>37.14985212485649</v>
       </c>
       <c r="G2" t="n">
         <v>33.76871875540306</v>
@@ -4324,49 +4324,49 @@
         <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>400.18</v>
       </c>
       <c r="L2" t="n">
-        <v>327.128108133742</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>697.388108133742</v>
+        <v>1140.7</v>
       </c>
       <c r="N2" t="n">
-        <v>697.388108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.183143567851</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1407.815317606416</v>
       </c>
       <c r="T2" t="n">
         <v>1221.067250178447</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698514</v>
+        <v>969.3617021698508</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861908</v>
+        <v>737.1889504861903</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165468</v>
+        <v>496.4076616165462</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138521</v>
+        <v>302.1835874138516</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190982</v>
+        <v>189.7417362190976</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>847.9629120561149</v>
+        <v>849.2675731951525</v>
       </c>
       <c r="C3" t="n">
-        <v>847.9629120561149</v>
+        <v>484.5201868865472</v>
       </c>
       <c r="D3" t="n">
-        <v>847.9629120561149</v>
+        <v>133.0679778989687</v>
       </c>
       <c r="E3" t="n">
-        <v>573.6316988789948</v>
+        <v>133.0679778989687</v>
       </c>
       <c r="F3" t="n">
-        <v>573.6316988789948</v>
+        <v>133.0679778989687</v>
       </c>
       <c r="G3" t="n">
-        <v>244.8234770117097</v>
+        <v>133.0679778989687</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>133.0679778989687</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.92</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.997993968056</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S3" t="n">
-        <v>1297.877982568697</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T3" t="n">
-        <v>1293.359351798195</v>
+        <v>916.8862351594544</v>
       </c>
       <c r="U3" t="n">
-        <v>1293.161446951808</v>
+        <v>916.6883303130679</v>
       </c>
       <c r="V3" t="n">
-        <v>1278.504207364414</v>
+        <v>902.0310907256738</v>
       </c>
       <c r="W3" t="n">
-        <v>1245.804063011052</v>
+        <v>869.3309463723117</v>
       </c>
       <c r="X3" t="n">
-        <v>1225.740689833893</v>
+        <v>849.2675731951525</v>
       </c>
       <c r="Y3" t="n">
-        <v>1225.740689833893</v>
+        <v>849.2675731951525</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>985.7272853098659</v>
+        <v>582.1191068155374</v>
       </c>
       <c r="C4" t="n">
-        <v>985.7272853098659</v>
+        <v>660.9745275363783</v>
       </c>
       <c r="D4" t="n">
-        <v>985.7272853098659</v>
+        <v>774.2936716613784</v>
       </c>
       <c r="E4" t="n">
-        <v>985.7272853098659</v>
+        <v>892.1225758727915</v>
       </c>
       <c r="F4" t="n">
-        <v>985.7272853098659</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="G4" t="n">
-        <v>985.7272853098659</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="H4" t="n">
-        <v>994.2194283582137</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="I4" t="n">
-        <v>994.2194283582137</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="J4" t="n">
-        <v>1364.479428358214</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.273682802524</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1258.790761928658</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.177358901337</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>774.2966876474056</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>460.7236912579127</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>179.6001272851838</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>368.4538490669395</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>615.0149741642425</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="V4" t="n">
-        <v>813.8363670501885</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="W4" t="n">
-        <v>985.7272853098659</v>
+        <v>431.0883157913439</v>
       </c>
       <c r="X4" t="n">
-        <v>985.7272853098659</v>
+        <v>582.1191068155374</v>
       </c>
       <c r="Y4" t="n">
-        <v>985.7272853098659</v>
+        <v>582.1191068155374</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>755.48</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>755.48</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>755.48</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="O5" t="n">
+        <v>1067.648108133742</v>
+      </c>
+      <c r="P5" t="n">
         <v>1125.74</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>737.7342977610062</v>
+        <v>1047.928564856972</v>
       </c>
       <c r="C6" t="n">
-        <v>372.9869114524009</v>
+        <v>1047.928564856972</v>
       </c>
       <c r="D6" t="n">
-        <v>372.9869114524009</v>
+        <v>1047.928564856972</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>701.7951333196861</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="G6" t="n">
         <v>29.92</v>
@@ -4682,7 +4682,7 @@
         <v>1075.987801776748</v>
       </c>
       <c r="Y6" t="n">
-        <v>1075.987801776748</v>
+        <v>1047.928564856972</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>760.6020042310051</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="C7" t="n">
-        <v>760.6020042310051</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="D7" t="n">
-        <v>760.6020042310051</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="E7" t="n">
-        <v>760.6020042310051</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="F7" t="n">
-        <v>884.9629768229406</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="G7" t="n">
-        <v>884.9629768229406</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="H7" t="n">
-        <v>884.9629768229406</v>
+        <v>663.0724028488492</v>
       </c>
       <c r="I7" t="n">
-        <v>884.9629768229406</v>
+        <v>881.2025562401257</v>
       </c>
       <c r="J7" t="n">
-        <v>1255.222976822941</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4746,22 +4746,22 @@
         <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>326.270994268102</v>
+        <v>228.741392885946</v>
       </c>
       <c r="W7" t="n">
-        <v>498.1619125277794</v>
+        <v>400.6323111456234</v>
       </c>
       <c r="X7" t="n">
-        <v>649.1927035519728</v>
+        <v>551.6631021698169</v>
       </c>
       <c r="Y7" t="n">
-        <v>760.6020042310051</v>
+        <v>663.0724028488492</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C8" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D8" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E8" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F8" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,22 +4795,22 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>755.48</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="M8" t="n">
-        <v>755.48</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1125.74</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1125.74</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W8" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1222.526720202428</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="C9" t="n">
-        <v>1222.526720202428</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="D9" t="n">
-        <v>1222.526720202428</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="E9" t="n">
-        <v>1035.178144962154</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="F9" t="n">
-        <v>692.1112335097536</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="G9" t="n">
-        <v>363.3030116424684</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4916,10 +4916,10 @@
         <v>1242.590093379587</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>864.8123156018096</v>
       </c>
       <c r="Y9" t="n">
-        <v>1222.526720202428</v>
+        <v>487.0345378240318</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>481.2138134849815</v>
+        <v>29.92</v>
       </c>
       <c r="C10" t="n">
-        <v>607.2158193034172</v>
+        <v>29.92</v>
       </c>
       <c r="D10" t="n">
-        <v>720.5349634284173</v>
+        <v>143.2391441250001</v>
       </c>
       <c r="E10" t="n">
-        <v>838.3638676398303</v>
+        <v>261.0680483364131</v>
       </c>
       <c r="F10" t="n">
-        <v>962.7248402317658</v>
+        <v>385.4290209283486</v>
       </c>
       <c r="G10" t="n">
-        <v>1116.313501200618</v>
+        <v>539.0176818972011</v>
       </c>
       <c r="H10" t="n">
-        <v>1116.313501200618</v>
+        <v>710.1532578762708</v>
       </c>
       <c r="I10" t="n">
-        <v>1116.313501200618</v>
+        <v>936.7622325500586</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1307.022232550059</v>
       </c>
       <c r="K10" t="n">
         <v>1386.743548464727</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>369.8045128059492</v>
+        <v>29.92</v>
       </c>
       <c r="Y10" t="n">
-        <v>481.2138134849815</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="11">
@@ -5008,40 +5008,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>602.3625378121178</v>
+        <v>602.4780217251043</v>
       </c>
       <c r="C11" t="n">
-        <v>471.5801355464673</v>
+        <v>471.6956194594539</v>
       </c>
       <c r="D11" t="n">
-        <v>380.3284630819726</v>
+        <v>380.4439469949592</v>
       </c>
       <c r="E11" t="n">
-        <v>295.1130190346305</v>
+        <v>295.2285029476171</v>
       </c>
       <c r="F11" t="n">
-        <v>209.365919329568</v>
+        <v>209.4814032425546</v>
       </c>
       <c r="G11" t="n">
-        <v>126.2121855844981</v>
+        <v>126.3276694974847</v>
       </c>
       <c r="H11" t="n">
-        <v>52.16</v>
+        <v>52.27548391298662</v>
       </c>
       <c r="I11" t="n">
         <v>52.16</v>
       </c>
       <c r="J11" t="n">
-        <v>138.0580950233907</v>
+        <v>564.059784243686</v>
       </c>
       <c r="K11" t="n">
-        <v>783.5380950233907</v>
+        <v>1209.539784243686</v>
       </c>
       <c r="L11" t="n">
-        <v>1429.018095023391</v>
+        <v>1855.019784243686</v>
       </c>
       <c r="M11" t="n">
-        <v>2074.498095023391</v>
+        <v>1855.019784243686</v>
       </c>
       <c r="N11" t="n">
         <v>2234.12041569551</v>
@@ -5059,25 +5059,25 @@
         <v>2608</v>
       </c>
       <c r="S11" t="n">
-        <v>2464.304619672302</v>
+        <v>2464.420103585289</v>
       </c>
       <c r="T11" t="n">
-        <v>2201.281287029369</v>
+        <v>2201.396770942356</v>
       </c>
       <c r="U11" t="n">
-        <v>1868.850496647289</v>
+        <v>1868.965980560276</v>
       </c>
       <c r="V11" t="n">
-        <v>1555.869664155548</v>
+        <v>1555.985148068535</v>
       </c>
       <c r="W11" t="n">
-        <v>1234.280294477823</v>
+        <v>1234.39577839081</v>
       </c>
       <c r="X11" t="n">
-        <v>959.248139467048</v>
+        <v>959.3636233800346</v>
       </c>
       <c r="Y11" t="n">
-        <v>765.9982074642132</v>
+        <v>766.1136913771999</v>
       </c>
     </row>
     <row r="12">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>497.6847528895822</v>
+        <v>702.7865405357536</v>
       </c>
       <c r="C12" t="n">
-        <v>132.9373665809768</v>
+        <v>661.2714774594715</v>
       </c>
       <c r="D12" t="n">
-        <v>104.7174808257216</v>
+        <v>427.9498040580448</v>
       </c>
       <c r="E12" t="n">
         <v>81.81637252075936</v>
@@ -5135,28 +5135,28 @@
         <v>2283.610055368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1897.096694318589</v>
+        <v>2102.198481964761</v>
       </c>
       <c r="S12" t="n">
-        <v>1763.459482614293</v>
+        <v>1968.561270260465</v>
       </c>
       <c r="T12" t="n">
-        <v>1680.365904254693</v>
+        <v>1885.467691900864</v>
       </c>
       <c r="U12" t="n">
-        <v>1599.396367999882</v>
+        <v>1481.265832413731</v>
       </c>
       <c r="V12" t="n">
-        <v>1180.698724372084</v>
+        <v>1062.568188785933</v>
       </c>
       <c r="W12" t="n">
-        <v>1067.190499210641</v>
+        <v>949.0599636244896</v>
       </c>
       <c r="X12" t="n">
-        <v>966.3190452254014</v>
+        <v>848.1885096392496</v>
       </c>
       <c r="Y12" t="n">
-        <v>562.8933959666798</v>
+        <v>767.9951836128512</v>
       </c>
     </row>
     <row r="13">
@@ -5184,13 +5184,13 @@
         <v>919.6094505196728</v>
       </c>
       <c r="H13" t="n">
-        <v>1014.467881576163</v>
+        <v>1015.592503547923</v>
       </c>
       <c r="I13" t="n">
-        <v>1175.567095594213</v>
+        <v>1176.691717565973</v>
       </c>
       <c r="J13" t="n">
-        <v>1502.510264279451</v>
+        <v>1503.634886251211</v>
       </c>
       <c r="K13" t="n">
         <v>1607.721180183533</v>
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>602.4780217251043</v>
+        <v>602.3625378121178</v>
       </c>
       <c r="C14" t="n">
-        <v>471.6956194594539</v>
+        <v>471.5801355464673</v>
       </c>
       <c r="D14" t="n">
-        <v>380.4439469949592</v>
+        <v>380.3284630819726</v>
       </c>
       <c r="E14" t="n">
-        <v>295.2285029476171</v>
+        <v>295.1130190346305</v>
       </c>
       <c r="F14" t="n">
-        <v>209.4814032425546</v>
+        <v>209.365919329568</v>
       </c>
       <c r="G14" t="n">
-        <v>126.3276694974847</v>
+        <v>126.2121855844981</v>
       </c>
       <c r="H14" t="n">
-        <v>52.27548391298662</v>
+        <v>52.16</v>
       </c>
       <c r="I14" t="n">
         <v>52.16</v>
       </c>
       <c r="J14" t="n">
-        <v>564.059784243686</v>
+        <v>138.0580950233907</v>
       </c>
       <c r="K14" t="n">
-        <v>1209.539784243686</v>
+        <v>555.1603950216642</v>
       </c>
       <c r="L14" t="n">
-        <v>1588.64041569551</v>
+        <v>1200.640395021664</v>
       </c>
       <c r="M14" t="n">
-        <v>2234.12041569551</v>
+        <v>1200.640395021664</v>
       </c>
       <c r="N14" t="n">
-        <v>2234.12041569551</v>
+        <v>1200.640395021664</v>
       </c>
       <c r="O14" t="n">
-        <v>2403.96790486741</v>
+        <v>1370.487884193564</v>
       </c>
       <c r="P14" t="n">
-        <v>2608</v>
+        <v>2015.967884193564</v>
       </c>
       <c r="Q14" t="n">
         <v>2608</v>
       </c>
       <c r="R14" t="n">
-        <v>2608</v>
+        <v>2607.884516087013</v>
       </c>
       <c r="S14" t="n">
-        <v>2464.420103585289</v>
+        <v>2464.304619672302</v>
       </c>
       <c r="T14" t="n">
-        <v>2201.396770942356</v>
+        <v>2201.281287029369</v>
       </c>
       <c r="U14" t="n">
-        <v>1868.965980560276</v>
+        <v>1868.850496647289</v>
       </c>
       <c r="V14" t="n">
-        <v>1555.985148068535</v>
+        <v>1555.869664155548</v>
       </c>
       <c r="W14" t="n">
-        <v>1234.39577839081</v>
+        <v>1234.280294477823</v>
       </c>
       <c r="X14" t="n">
-        <v>959.3636233800346</v>
+        <v>959.248139467048</v>
       </c>
       <c r="Y14" t="n">
-        <v>766.1136913771999</v>
+        <v>765.9982074642132</v>
       </c>
     </row>
     <row r="15">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1026.018863768077</v>
+        <v>174.4524296572589</v>
       </c>
       <c r="C15" t="n">
-        <v>984.503800691795</v>
+        <v>132.9373665809768</v>
       </c>
       <c r="D15" t="n">
-        <v>633.0515917042167</v>
+        <v>104.7174808257216</v>
       </c>
       <c r="E15" t="n">
-        <v>286.9181601669312</v>
+        <v>81.81637252075936</v>
       </c>
       <c r="F15" t="n">
         <v>61.98178430068172</v>
@@ -5387,13 +5387,13 @@
         <v>1709.032835250579</v>
       </c>
       <c r="W15" t="n">
-        <v>1595.524610089136</v>
+        <v>1272.292286856813</v>
       </c>
       <c r="X15" t="n">
-        <v>1494.653156103896</v>
+        <v>848.1885096392498</v>
       </c>
       <c r="Y15" t="n">
-        <v>1414.459830077498</v>
+        <v>444.7628603805282</v>
       </c>
     </row>
     <row r="16">
@@ -5460,10 +5460,10 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U16" t="n">
-        <v>330.020162612217</v>
+        <v>331.1447845839767</v>
       </c>
       <c r="V16" t="n">
-        <v>449.641555498163</v>
+        <v>450.7661774699227</v>
       </c>
       <c r="W16" t="n">
         <v>542.3324737578404</v>
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>602.4780217251043</v>
+        <v>602.3625378121177</v>
       </c>
       <c r="C17" t="n">
-        <v>471.6956194594539</v>
+        <v>471.5801355464673</v>
       </c>
       <c r="D17" t="n">
-        <v>380.4439469949592</v>
+        <v>380.3284630819725</v>
       </c>
       <c r="E17" t="n">
-        <v>295.2285029476171</v>
+        <v>295.1130190346304</v>
       </c>
       <c r="F17" t="n">
-        <v>209.4814032425546</v>
+        <v>209.365919329568</v>
       </c>
       <c r="G17" t="n">
-        <v>126.3276694974847</v>
+        <v>126.212185584498</v>
       </c>
       <c r="H17" t="n">
-        <v>52.27548391298663</v>
+        <v>52.16</v>
       </c>
       <c r="I17" t="n">
         <v>52.16</v>
@@ -5539,19 +5539,19 @@
         <v>2201.396770942356</v>
       </c>
       <c r="U17" t="n">
-        <v>1868.965980560276</v>
+        <v>1868.850496647289</v>
       </c>
       <c r="V17" t="n">
-        <v>1555.985148068535</v>
+        <v>1555.869664155548</v>
       </c>
       <c r="W17" t="n">
-        <v>1234.39577839081</v>
+        <v>1234.280294477823</v>
       </c>
       <c r="X17" t="n">
-        <v>959.3636233800346</v>
+        <v>959.248139467048</v>
       </c>
       <c r="Y17" t="n">
-        <v>766.1136913771999</v>
+        <v>765.9982074642132</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1144.149399354229</v>
+        <v>303.7368540521363</v>
       </c>
       <c r="C18" t="n">
-        <v>1102.634336277946</v>
+        <v>132.9373665809768</v>
       </c>
       <c r="D18" t="n">
-        <v>751.182127290368</v>
+        <v>104.7174808257216</v>
       </c>
       <c r="E18" t="n">
-        <v>405.0486957530826</v>
+        <v>81.81637252075936</v>
       </c>
       <c r="F18" t="n">
         <v>61.98178430068171</v>
@@ -5606,31 +5606,31 @@
         <v>2283.610055368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2283.610055368536</v>
+        <v>2207.792692117242</v>
       </c>
       <c r="R18" t="n">
-        <v>2102.198481964761</v>
+        <v>2026.381118713466</v>
       </c>
       <c r="S18" t="n">
-        <v>1968.561270260465</v>
+        <v>1892.74390700917</v>
       </c>
       <c r="T18" t="n">
-        <v>1885.467691900864</v>
+        <v>1809.65032864957</v>
       </c>
       <c r="U18" t="n">
-        <v>1804.498155646054</v>
+        <v>1728.68079239476</v>
       </c>
       <c r="V18" t="n">
-        <v>1709.032835250579</v>
+        <v>1633.215471999285</v>
       </c>
       <c r="W18" t="n">
-        <v>1595.524610089136</v>
+        <v>1519.707246837842</v>
       </c>
       <c r="X18" t="n">
-        <v>1494.653156103896</v>
+        <v>1095.603469620279</v>
       </c>
       <c r="Y18" t="n">
-        <v>1414.459830077498</v>
+        <v>692.1778203615571</v>
       </c>
     </row>
     <row r="19">
@@ -5709,7 +5709,7 @@
         <v>615.2878867537937</v>
       </c>
       <c r="Y19" t="n">
-        <v>646.3725654610662</v>
+        <v>647.497187432826</v>
       </c>
     </row>
     <row r="20">
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>174.4524296572589</v>
+        <v>1144.149399354229</v>
       </c>
       <c r="C21" t="n">
-        <v>132.9373665809768</v>
+        <v>779.4020130456233</v>
       </c>
       <c r="D21" t="n">
-        <v>104.7174808257216</v>
+        <v>427.9498040580448</v>
       </c>
       <c r="E21" t="n">
         <v>81.81637252075936</v>
@@ -5855,19 +5855,19 @@
         <v>1885.467691900864</v>
       </c>
       <c r="U21" t="n">
-        <v>1599.396367999882</v>
+        <v>1804.498155646054</v>
       </c>
       <c r="V21" t="n">
-        <v>1180.698724372084</v>
+        <v>1709.032835250579</v>
       </c>
       <c r="W21" t="n">
-        <v>743.958175978318</v>
+        <v>1595.524610089136</v>
       </c>
       <c r="X21" t="n">
-        <v>643.0867219930781</v>
+        <v>1494.653156103896</v>
       </c>
       <c r="Y21" t="n">
-        <v>562.8933959666797</v>
+        <v>1414.459830077498</v>
       </c>
     </row>
     <row r="22">
@@ -5877,19 +5877,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>680.0545250991181</v>
+        <v>678.9299031273583</v>
       </c>
       <c r="C22" t="n">
-        <v>726.8565309175539</v>
+        <v>725.7319089457941</v>
       </c>
       <c r="D22" t="n">
-        <v>760.9756750425539</v>
+        <v>759.8510530707941</v>
       </c>
       <c r="E22" t="n">
-        <v>799.6045792539669</v>
+        <v>798.4799572822071</v>
       </c>
       <c r="F22" t="n">
-        <v>844.7655518459023</v>
+        <v>843.6409298741427</v>
       </c>
       <c r="G22" t="n">
         <v>918.4848285479131</v>
@@ -5934,19 +5934,19 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U22" t="n">
-        <v>331.1447845839767</v>
+        <v>330.020162612217</v>
       </c>
       <c r="V22" t="n">
-        <v>450.7661774699227</v>
+        <v>449.641555498163</v>
       </c>
       <c r="W22" t="n">
-        <v>543.4570957296002</v>
+        <v>542.3324737578404</v>
       </c>
       <c r="X22" t="n">
-        <v>615.2878867537937</v>
+        <v>614.1632647820339</v>
       </c>
       <c r="Y22" t="n">
-        <v>647.497187432826</v>
+        <v>646.3725654610662</v>
       </c>
     </row>
     <row r="23">
@@ -5974,7 +5974,7 @@
         <v>126.3276694974847</v>
       </c>
       <c r="H23" t="n">
-        <v>52.16</v>
+        <v>52.27548391298662</v>
       </c>
       <c r="I23" t="n">
         <v>52.16</v>
@@ -5983,7 +5983,7 @@
         <v>138.0580950233907</v>
       </c>
       <c r="K23" t="n">
-        <v>718.9437132834502</v>
+        <v>318.7922512545465</v>
       </c>
       <c r="L23" t="n">
         <v>943.1604156955104</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1144.149399354229</v>
+        <v>1349.2511870004</v>
       </c>
       <c r="C24" t="n">
-        <v>779.4020130456233</v>
+        <v>1102.634336277947</v>
       </c>
       <c r="D24" t="n">
-        <v>427.9498040580448</v>
+        <v>751.1821272903682</v>
       </c>
       <c r="E24" t="n">
-        <v>81.81637252075936</v>
+        <v>405.0486957530827</v>
       </c>
       <c r="F24" t="n">
-        <v>61.98178430068171</v>
+        <v>61.98178430068172</v>
       </c>
       <c r="G24" t="n">
-        <v>56.95991654050543</v>
+        <v>56.95991654050545</v>
       </c>
       <c r="H24" t="n">
         <v>52.16</v>
@@ -6117,28 +6117,28 @@
         <v>680.0545250991181</v>
       </c>
       <c r="C25" t="n">
-        <v>725.7319089457941</v>
+        <v>726.8565309175539</v>
       </c>
       <c r="D25" t="n">
-        <v>759.8510530707941</v>
+        <v>760.9756750425539</v>
       </c>
       <c r="E25" t="n">
-        <v>798.4799572822071</v>
+        <v>799.6045792539669</v>
       </c>
       <c r="F25" t="n">
-        <v>843.6409298741427</v>
+        <v>844.7655518459023</v>
       </c>
       <c r="G25" t="n">
-        <v>918.4848285479131</v>
+        <v>919.6094505196728</v>
       </c>
       <c r="H25" t="n">
-        <v>1014.467881576163</v>
+        <v>1015.592503547923</v>
       </c>
       <c r="I25" t="n">
         <v>1175.567095594213</v>
       </c>
       <c r="J25" t="n">
-        <v>1502.510264279452</v>
+        <v>1502.510264279451</v>
       </c>
       <c r="K25" t="n">
         <v>1607.721180183533</v>
@@ -6156,13 +6156,13 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P25" t="n">
-        <v>820.5867150304003</v>
+        <v>820.5867150304002</v>
       </c>
       <c r="Q25" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R25" t="n">
-        <v>83.62900582669619</v>
+        <v>83.6290058266962</v>
       </c>
       <c r="S25" t="n">
         <v>52.16</v>
@@ -6171,10 +6171,10 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U25" t="n">
-        <v>331.1447845839768</v>
+        <v>331.1447845839767</v>
       </c>
       <c r="V25" t="n">
-        <v>450.7661774699228</v>
+        <v>450.7661774699227</v>
       </c>
       <c r="W25" t="n">
         <v>543.4570957296002</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>602.4780217251043</v>
+        <v>602.3625378121178</v>
       </c>
       <c r="C26" t="n">
-        <v>471.6956194594539</v>
+        <v>471.5801355464673</v>
       </c>
       <c r="D26" t="n">
-        <v>380.4439469949592</v>
+        <v>380.3284630819726</v>
       </c>
       <c r="E26" t="n">
-        <v>295.2285029476171</v>
+        <v>295.1130190346305</v>
       </c>
       <c r="F26" t="n">
-        <v>209.4814032425546</v>
+        <v>209.365919329568</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3276694974847</v>
+        <v>126.2121855844981</v>
       </c>
       <c r="H26" t="n">
         <v>52.16</v>
@@ -6220,19 +6220,19 @@
         <v>564.059784243686</v>
       </c>
       <c r="K26" t="n">
-        <v>744.7939404748417</v>
+        <v>1209.539784243686</v>
       </c>
       <c r="L26" t="n">
-        <v>1200.640395021664</v>
+        <v>1642.088299889074</v>
       </c>
       <c r="M26" t="n">
-        <v>1200.640395021664</v>
+        <v>1642.088299889074</v>
       </c>
       <c r="N26" t="n">
-        <v>1200.640395021664</v>
+        <v>1642.088299889074</v>
       </c>
       <c r="O26" t="n">
-        <v>1370.487884193564</v>
+        <v>1811.935789060974</v>
       </c>
       <c r="P26" t="n">
         <v>2015.967884193564</v>
@@ -6241,28 +6241,28 @@
         <v>2608</v>
       </c>
       <c r="R26" t="n">
-        <v>2608</v>
+        <v>2607.884516087013</v>
       </c>
       <c r="S26" t="n">
-        <v>2464.420103585289</v>
+        <v>2464.304619672302</v>
       </c>
       <c r="T26" t="n">
-        <v>2201.396770942356</v>
+        <v>2201.281287029369</v>
       </c>
       <c r="U26" t="n">
-        <v>1868.965980560276</v>
+        <v>1868.850496647289</v>
       </c>
       <c r="V26" t="n">
-        <v>1555.985148068535</v>
+        <v>1555.869664155548</v>
       </c>
       <c r="W26" t="n">
-        <v>1234.39577839081</v>
+        <v>1234.280294477823</v>
       </c>
       <c r="X26" t="n">
-        <v>959.3636233800346</v>
+        <v>959.248139467048</v>
       </c>
       <c r="Y26" t="n">
-        <v>766.1136913771999</v>
+        <v>765.9982074642132</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>820.9170761219054</v>
+        <v>626.9691772844596</v>
       </c>
       <c r="C27" t="n">
-        <v>779.4020130456233</v>
+        <v>585.4541142081775</v>
       </c>
       <c r="D27" t="n">
-        <v>751.1821272903682</v>
+        <v>557.2342284529224</v>
       </c>
       <c r="E27" t="n">
-        <v>728.2810189854059</v>
+        <v>405.0486957530827</v>
       </c>
       <c r="F27" t="n">
-        <v>708.4464307653283</v>
+        <v>61.98178430068172</v>
       </c>
       <c r="G27" t="n">
-        <v>380.1922397728287</v>
+        <v>56.95991654050545</v>
       </c>
       <c r="H27" t="n">
         <v>52.16</v>
@@ -6317,31 +6317,31 @@
         <v>2283.610055368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2283.610055368536</v>
+        <v>2207.792692117242</v>
       </c>
       <c r="R27" t="n">
-        <v>1778.966158732437</v>
+        <v>2026.381118713466</v>
       </c>
       <c r="S27" t="n">
-        <v>1645.328947028141</v>
+        <v>1892.74390700917</v>
       </c>
       <c r="T27" t="n">
-        <v>1562.235368668541</v>
+        <v>1809.65032864957</v>
       </c>
       <c r="U27" t="n">
-        <v>1481.265832413731</v>
+        <v>1728.68079239476</v>
       </c>
       <c r="V27" t="n">
-        <v>1180.698724372084</v>
+        <v>1633.215471999285</v>
       </c>
       <c r="W27" t="n">
-        <v>1067.190499210641</v>
+        <v>1519.707246837842</v>
       </c>
       <c r="X27" t="n">
-        <v>966.3190452254014</v>
+        <v>1418.835792852602</v>
       </c>
       <c r="Y27" t="n">
-        <v>886.125719199003</v>
+        <v>1015.41014359388</v>
       </c>
     </row>
     <row r="28">
@@ -6369,13 +6369,13 @@
         <v>919.6094505196728</v>
       </c>
       <c r="H28" t="n">
-        <v>1015.592503547923</v>
+        <v>1014.467881576163</v>
       </c>
       <c r="I28" t="n">
-        <v>1176.691717565973</v>
+        <v>1175.567095594213</v>
       </c>
       <c r="J28" t="n">
-        <v>1502.510264279452</v>
+        <v>1502.510264279451</v>
       </c>
       <c r="K28" t="n">
         <v>1607.721180183533</v>
@@ -6393,13 +6393,13 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P28" t="n">
-        <v>820.5867150304003</v>
+        <v>820.5867150304002</v>
       </c>
       <c r="Q28" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R28" t="n">
-        <v>83.62900582669619</v>
+        <v>83.6290058266962</v>
       </c>
       <c r="S28" t="n">
         <v>52.16</v>
@@ -6408,10 +6408,10 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U28" t="n">
-        <v>331.1447845839768</v>
+        <v>331.1447845839767</v>
       </c>
       <c r="V28" t="n">
-        <v>450.7661774699228</v>
+        <v>450.7661774699227</v>
       </c>
       <c r="W28" t="n">
         <v>543.4570957296002</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>602.3625378121177</v>
+        <v>602.4780217251043</v>
       </c>
       <c r="C29" t="n">
-        <v>471.5801355464673</v>
+        <v>471.6956194594539</v>
       </c>
       <c r="D29" t="n">
-        <v>380.3284630819725</v>
+        <v>380.4439469949592</v>
       </c>
       <c r="E29" t="n">
-        <v>295.1130190346304</v>
+        <v>295.2285029476171</v>
       </c>
       <c r="F29" t="n">
-        <v>209.365919329568</v>
+        <v>209.4814032425546</v>
       </c>
       <c r="G29" t="n">
-        <v>126.212185584498</v>
+        <v>126.3276694974847</v>
       </c>
       <c r="H29" t="n">
         <v>52.16</v>
@@ -6454,7 +6454,7 @@
         <v>52.16</v>
       </c>
       <c r="J29" t="n">
-        <v>138.0580950233907</v>
+        <v>564.059784243686</v>
       </c>
       <c r="K29" t="n">
         <v>772.3915974770139</v>
@@ -6478,28 +6478,28 @@
         <v>2608</v>
       </c>
       <c r="R29" t="n">
-        <v>2607.884516087013</v>
+        <v>2608</v>
       </c>
       <c r="S29" t="n">
-        <v>2464.304619672302</v>
+        <v>2464.420103585289</v>
       </c>
       <c r="T29" t="n">
-        <v>2201.281287029369</v>
+        <v>2201.396770942356</v>
       </c>
       <c r="U29" t="n">
-        <v>1868.850496647289</v>
+        <v>1868.965980560276</v>
       </c>
       <c r="V29" t="n">
-        <v>1555.869664155548</v>
+        <v>1555.985148068535</v>
       </c>
       <c r="W29" t="n">
-        <v>1234.280294477823</v>
+        <v>1234.39577839081</v>
       </c>
       <c r="X29" t="n">
-        <v>959.248139467048</v>
+        <v>959.3636233800346</v>
       </c>
       <c r="Y29" t="n">
-        <v>765.9982074642132</v>
+        <v>766.1136913771999</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1349.2511870004</v>
+        <v>174.4524296572589</v>
       </c>
       <c r="C30" t="n">
-        <v>1307.736123924118</v>
+        <v>132.9373665809768</v>
       </c>
       <c r="D30" t="n">
-        <v>956.28391493654</v>
+        <v>104.7174808257216</v>
       </c>
       <c r="E30" t="n">
-        <v>920.8953405451823</v>
+        <v>81.81637252075936</v>
       </c>
       <c r="F30" t="n">
-        <v>577.8284290927814</v>
+        <v>61.98178430068171</v>
       </c>
       <c r="G30" t="n">
-        <v>572.8065613326052</v>
+        <v>56.95991654050543</v>
       </c>
       <c r="H30" t="n">
-        <v>244.7743215597765</v>
+        <v>52.16</v>
       </c>
       <c r="I30" t="n">
         <v>52.16</v>
@@ -6557,28 +6557,28 @@
         <v>2283.610055368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2102.198481964761</v>
+        <v>1897.096694318589</v>
       </c>
       <c r="S30" t="n">
-        <v>1968.561270260465</v>
+        <v>1763.459482614293</v>
       </c>
       <c r="T30" t="n">
-        <v>1885.467691900864</v>
+        <v>1680.365904254693</v>
       </c>
       <c r="U30" t="n">
-        <v>1804.498155646054</v>
+        <v>1599.396367999882</v>
       </c>
       <c r="V30" t="n">
-        <v>1709.032835250579</v>
+        <v>1180.698724372084</v>
       </c>
       <c r="W30" t="n">
-        <v>1595.524610089136</v>
+        <v>743.958175978318</v>
       </c>
       <c r="X30" t="n">
-        <v>1494.653156103896</v>
+        <v>319.8543987607548</v>
       </c>
       <c r="Y30" t="n">
-        <v>1414.459830077498</v>
+        <v>239.6610727343565</v>
       </c>
     </row>
     <row r="31">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>602.3625378121178</v>
+        <v>602.3625378121177</v>
       </c>
       <c r="C32" t="n">
         <v>471.5801355464673</v>
       </c>
       <c r="D32" t="n">
-        <v>380.3284630819726</v>
+        <v>380.3284630819725</v>
       </c>
       <c r="E32" t="n">
-        <v>295.1130190346305</v>
+        <v>295.1130190346304</v>
       </c>
       <c r="F32" t="n">
         <v>209.365919329568</v>
       </c>
       <c r="G32" t="n">
-        <v>126.2121855844981</v>
+        <v>126.212185584498</v>
       </c>
       <c r="H32" t="n">
         <v>52.16</v>
@@ -6703,13 +6703,13 @@
         <v>2074.498095023391</v>
       </c>
       <c r="N32" t="n">
-        <v>2074.498095023391</v>
+        <v>2234.12041569551</v>
       </c>
       <c r="O32" t="n">
-        <v>2244.34558419529</v>
+        <v>2403.96790486741</v>
       </c>
       <c r="P32" t="n">
-        <v>2448.37767932788</v>
+        <v>2608</v>
       </c>
       <c r="Q32" t="n">
         <v>2608</v>
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1144.149399354229</v>
+        <v>379.5542173034306</v>
       </c>
       <c r="C33" t="n">
-        <v>779.4020130456233</v>
+        <v>132.9373665809768</v>
       </c>
       <c r="D33" t="n">
-        <v>427.9498040580449</v>
+        <v>104.7174808257216</v>
       </c>
       <c r="E33" t="n">
-        <v>405.0486957530827</v>
+        <v>81.81637252075936</v>
       </c>
       <c r="F33" t="n">
-        <v>61.98178430068172</v>
+        <v>61.98178430068171</v>
       </c>
       <c r="G33" t="n">
-        <v>56.95991654050545</v>
+        <v>56.95991654050543</v>
       </c>
       <c r="H33" t="n">
         <v>52.16</v>
@@ -6806,16 +6806,16 @@
         <v>1804.498155646054</v>
       </c>
       <c r="V33" t="n">
-        <v>1709.032835250579</v>
+        <v>1385.800512018256</v>
       </c>
       <c r="W33" t="n">
-        <v>1595.524610089136</v>
+        <v>949.0599636244897</v>
       </c>
       <c r="X33" t="n">
-        <v>1494.653156103896</v>
+        <v>848.1885096392498</v>
       </c>
       <c r="Y33" t="n">
-        <v>1414.459830077498</v>
+        <v>767.9951836128514</v>
       </c>
     </row>
     <row r="34">
@@ -6849,7 +6849,7 @@
         <v>1175.567095594213</v>
       </c>
       <c r="J34" t="n">
-        <v>1502.510264279451</v>
+        <v>1502.510264279452</v>
       </c>
       <c r="K34" t="n">
         <v>1607.721180183533</v>
@@ -6867,13 +6867,13 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P34" t="n">
-        <v>820.5867150304002</v>
+        <v>820.5867150304003</v>
       </c>
       <c r="Q34" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R34" t="n">
-        <v>83.6290058266962</v>
+        <v>83.62900582669619</v>
       </c>
       <c r="S34" t="n">
         <v>52.16</v>
@@ -6882,10 +6882,10 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U34" t="n">
-        <v>331.1447845839767</v>
+        <v>331.1447845839768</v>
       </c>
       <c r="V34" t="n">
-        <v>450.7661774699227</v>
+        <v>450.7661774699228</v>
       </c>
       <c r="W34" t="n">
         <v>543.4570957296002</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>278.6800419271243</v>
+        <v>272.3310226606025</v>
       </c>
       <c r="C35" t="n">
-        <v>200.4228921867264</v>
+        <v>194.0738729202046</v>
       </c>
       <c r="D35" t="n">
-        <v>161.6964722474841</v>
+        <v>155.3474529809624</v>
       </c>
       <c r="E35" t="n">
-        <v>129.0062807253946</v>
+        <v>122.6572614588729</v>
       </c>
       <c r="F35" t="n">
-        <v>95.78443354558463</v>
+        <v>89.43541427906291</v>
       </c>
       <c r="G35" t="n">
-        <v>65.15595232576723</v>
+        <v>58.8069330592455</v>
       </c>
       <c r="H35" t="n">
-        <v>43.62901926652173</v>
+        <v>37.28</v>
       </c>
       <c r="I35" t="n">
         <v>37.28</v>
@@ -6931,19 +6931,19 @@
         <v>123.1780950233907</v>
       </c>
       <c r="K35" t="n">
-        <v>584.5180950233907</v>
+        <v>567.4404156955106</v>
       </c>
       <c r="L35" t="n">
-        <v>1045.858095023391</v>
+        <v>1028.780415695511</v>
       </c>
       <c r="M35" t="n">
-        <v>1045.858095023391</v>
+        <v>1490.12041569551</v>
       </c>
       <c r="N35" t="n">
-        <v>1232.8125108281</v>
+        <v>1490.12041569551</v>
       </c>
       <c r="O35" t="n">
-        <v>1402.66</v>
+        <v>1659.96790486741</v>
       </c>
       <c r="P35" t="n">
         <v>1864</v>
@@ -6952,28 +6952,28 @@
         <v>1864</v>
       </c>
       <c r="R35" t="n">
-        <v>1864</v>
+        <v>1857.650980733478</v>
       </c>
       <c r="S35" t="n">
-        <v>1772.945356110541</v>
+        <v>1766.59633684402</v>
       </c>
       <c r="T35" t="n">
-        <v>1562.447275992861</v>
+        <v>1556.098256726339</v>
       </c>
       <c r="U35" t="n">
-        <v>1282.541738136033</v>
+        <v>1276.192718869512</v>
       </c>
       <c r="V35" t="n">
-        <v>1022.086158169545</v>
+        <v>1015.737138903023</v>
       </c>
       <c r="W35" t="n">
-        <v>753.0220410170723</v>
+        <v>746.6730217505506</v>
       </c>
       <c r="X35" t="n">
-        <v>530.5151385315494</v>
+        <v>524.1661192650276</v>
       </c>
       <c r="Y35" t="n">
-        <v>389.7904590539672</v>
+        <v>383.4414397874455</v>
       </c>
     </row>
     <row r="36">
@@ -6983,13 +6983,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>402.0273863086054</v>
+        <v>1099.613026833469</v>
       </c>
       <c r="C36" t="n">
-        <v>37.28</v>
+        <v>734.8656405248639</v>
       </c>
       <c r="D36" t="n">
-        <v>37.28</v>
+        <v>383.4134315372855</v>
       </c>
       <c r="E36" t="n">
         <v>37.28</v>
@@ -7007,19 +7007,19 @@
         <v>37.28</v>
       </c>
       <c r="J36" t="n">
-        <v>233.0594978168084</v>
+        <v>212.5378855434729</v>
       </c>
       <c r="K36" t="n">
-        <v>545.0092224960974</v>
+        <v>524.487610222762</v>
       </c>
       <c r="L36" t="n">
-        <v>597.2130537319465</v>
+        <v>576.6914414586111</v>
       </c>
       <c r="M36" t="n">
-        <v>875.9129454748057</v>
+        <v>855.3913332014703</v>
       </c>
       <c r="N36" t="n">
-        <v>1206.91064112011</v>
+        <v>1186.389028846774</v>
       </c>
       <c r="O36" t="n">
         <v>1606.304284398418</v>
@@ -7034,25 +7034,25 @@
         <v>1735.113679121477</v>
       </c>
       <c r="S36" t="n">
-        <v>1654.001719942434</v>
+        <v>1351.246342416766</v>
       </c>
       <c r="T36" t="n">
-        <v>1623.433394108086</v>
+        <v>1320.678016582418</v>
       </c>
       <c r="U36" t="n">
-        <v>1594.989110378528</v>
+        <v>1292.233732852861</v>
       </c>
       <c r="V36" t="n">
-        <v>1552.049042508306</v>
+        <v>1249.293664982638</v>
       </c>
       <c r="W36" t="n">
-        <v>1242.240203336735</v>
+        <v>1188.310692346448</v>
       </c>
       <c r="X36" t="n">
-        <v>1193.894001876748</v>
+        <v>1139.96449088646</v>
       </c>
       <c r="Y36" t="n">
-        <v>790.4683526180263</v>
+        <v>1112.296417385314</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>400.3168745045214</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="C37" t="n">
-        <v>400.3168745045214</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="D37" t="n">
-        <v>485.9160186295215</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="E37" t="n">
-        <v>576.0249228409346</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="F37" t="n">
-        <v>576.0249228409346</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="G37" t="n">
-        <v>702.348821514705</v>
+        <v>299.4267857346181</v>
       </c>
       <c r="H37" t="n">
-        <v>849.811874542955</v>
+        <v>446.8898387628681</v>
       </c>
       <c r="I37" t="n">
-        <v>1062.391088561005</v>
+        <v>659.4690527809182</v>
       </c>
       <c r="J37" t="n">
-        <v>1072.534257246243</v>
+        <v>1037.892221466156</v>
       </c>
       <c r="K37" t="n">
-        <v>1229.225173150325</v>
+        <v>1194.583137370238</v>
       </c>
       <c r="L37" t="n">
         <v>1238.304989100594</v>
@@ -7113,25 +7113,25 @@
         <v>37.28</v>
       </c>
       <c r="S37" t="n">
-        <v>37.28</v>
+        <v>57.91722738925508</v>
       </c>
       <c r="T37" t="n">
-        <v>37.28</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="U37" t="n">
-        <v>256.145956244844</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="V37" t="n">
-        <v>256.145956244844</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="W37" t="n">
-        <v>400.3168745045214</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="X37" t="n">
-        <v>400.3168745045214</v>
+        <v>173.1028870608476</v>
       </c>
       <c r="Y37" t="n">
-        <v>400.3168745045214</v>
+        <v>173.1028870608476</v>
       </c>
     </row>
     <row r="38">
@@ -7141,34 +7141,34 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>278.6800419271243</v>
+        <v>272.3310226606025</v>
       </c>
       <c r="C38" t="n">
-        <v>200.4228921867264</v>
+        <v>194.0738729202046</v>
       </c>
       <c r="D38" t="n">
-        <v>161.6964722474841</v>
+        <v>155.3474529809624</v>
       </c>
       <c r="E38" t="n">
-        <v>129.0062807253946</v>
+        <v>122.6572614588729</v>
       </c>
       <c r="F38" t="n">
-        <v>95.78443354558463</v>
+        <v>89.43541427906291</v>
       </c>
       <c r="G38" t="n">
-        <v>65.15595232576723</v>
+        <v>58.8069330592455</v>
       </c>
       <c r="H38" t="n">
-        <v>43.62901926652172</v>
+        <v>37.28</v>
       </c>
       <c r="I38" t="n">
         <v>37.28</v>
       </c>
       <c r="J38" t="n">
-        <v>123.1780950233907</v>
+        <v>498.62</v>
       </c>
       <c r="K38" t="n">
-        <v>584.5180950233907</v>
+        <v>804.5637132834503</v>
       </c>
       <c r="L38" t="n">
         <v>1028.780415695511</v>
@@ -7189,28 +7189,28 @@
         <v>1864</v>
       </c>
       <c r="R38" t="n">
-        <v>1864</v>
+        <v>1857.650980733478</v>
       </c>
       <c r="S38" t="n">
-        <v>1772.945356110541</v>
+        <v>1766.59633684402</v>
       </c>
       <c r="T38" t="n">
-        <v>1562.447275992861</v>
+        <v>1556.098256726339</v>
       </c>
       <c r="U38" t="n">
-        <v>1282.541738136033</v>
+        <v>1276.192718869512</v>
       </c>
       <c r="V38" t="n">
-        <v>1022.086158169545</v>
+        <v>1015.737138903023</v>
       </c>
       <c r="W38" t="n">
-        <v>753.0220410170723</v>
+        <v>746.6730217505506</v>
       </c>
       <c r="X38" t="n">
-        <v>530.5151385315494</v>
+        <v>524.1661192650276</v>
       </c>
       <c r="Y38" t="n">
-        <v>389.7904590539672</v>
+        <v>383.4414397874455</v>
       </c>
     </row>
     <row r="39">
@@ -7220,43 +7220,43 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>275.0956770864095</v>
+        <v>572.9612330121774</v>
       </c>
       <c r="C39" t="n">
-        <v>275.0956770864095</v>
+        <v>572.9612330121774</v>
       </c>
       <c r="D39" t="n">
-        <v>37.28</v>
+        <v>572.9612330121774</v>
       </c>
       <c r="E39" t="n">
-        <v>37.28</v>
+        <v>572.9612330121774</v>
       </c>
       <c r="F39" t="n">
-        <v>37.28</v>
+        <v>229.8943215597765</v>
       </c>
       <c r="G39" t="n">
-        <v>37.28</v>
+        <v>229.8943215597765</v>
       </c>
       <c r="H39" t="n">
-        <v>37.28</v>
+        <v>229.8943215597765</v>
       </c>
       <c r="I39" t="n">
         <v>37.28</v>
       </c>
       <c r="J39" t="n">
-        <v>37.28</v>
+        <v>207.1844232611675</v>
       </c>
       <c r="K39" t="n">
-        <v>349.2297246792891</v>
+        <v>519.1341479404566</v>
       </c>
       <c r="L39" t="n">
-        <v>576.6914414586111</v>
+        <v>955.5464222715058</v>
       </c>
       <c r="M39" t="n">
-        <v>855.3913332014703</v>
+        <v>1234.246314014365</v>
       </c>
       <c r="N39" t="n">
-        <v>1186.389028846774</v>
+        <v>1565.244009659669</v>
       </c>
       <c r="O39" t="n">
         <v>1606.304284398418</v>
@@ -7274,22 +7274,22 @@
         <v>1654.001719942434</v>
       </c>
       <c r="T39" t="n">
-        <v>1623.433394108086</v>
+        <v>1247.67581835051</v>
       </c>
       <c r="U39" t="n">
-        <v>1594.989110378528</v>
+        <v>843.4739588633765</v>
       </c>
       <c r="V39" t="n">
-        <v>1552.049042508306</v>
+        <v>800.5338909931542</v>
       </c>
       <c r="W39" t="n">
-        <v>1491.066069872115</v>
+        <v>739.5509183569637</v>
       </c>
       <c r="X39" t="n">
-        <v>1066.962292654552</v>
+        <v>691.2047168969763</v>
       </c>
       <c r="Y39" t="n">
-        <v>663.5366433958303</v>
+        <v>663.5366433958304</v>
       </c>
     </row>
     <row r="40">
@@ -7299,49 +7299,49 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>37.28</v>
+        <v>857.5307936685714</v>
       </c>
       <c r="C40" t="n">
-        <v>37.28</v>
+        <v>955.8127994870072</v>
       </c>
       <c r="D40" t="n">
-        <v>122.8791441250001</v>
+        <v>1041.411943612007</v>
       </c>
       <c r="E40" t="n">
-        <v>212.9880483364131</v>
+        <v>1131.52084782342</v>
       </c>
       <c r="F40" t="n">
-        <v>212.9880483364131</v>
+        <v>1228.161820415356</v>
       </c>
       <c r="G40" t="n">
-        <v>339.3119470101836</v>
+        <v>1228.161820415356</v>
       </c>
       <c r="H40" t="n">
-        <v>486.7750000384336</v>
+        <v>1228.161820415356</v>
       </c>
       <c r="I40" t="n">
-        <v>699.3542140564838</v>
+        <v>1228.161820415356</v>
       </c>
       <c r="J40" t="n">
-        <v>1037.892221466156</v>
+        <v>1238.304989100594</v>
       </c>
       <c r="K40" t="n">
-        <v>1194.583137370237</v>
+        <v>1238.304989100594</v>
       </c>
       <c r="L40" t="n">
         <v>1238.304989100594</v>
       </c>
       <c r="M40" t="n">
-        <v>1190.105331946171</v>
+        <v>1190.105331946172</v>
       </c>
       <c r="N40" t="n">
-        <v>1088.417824220177</v>
+        <v>1088.417824220178</v>
       </c>
       <c r="O40" t="n">
-        <v>909.1738532180264</v>
+        <v>909.1738532180266</v>
       </c>
       <c r="P40" t="n">
-        <v>669.187204153199</v>
+        <v>669.1872041531991</v>
       </c>
       <c r="Q40" t="n">
         <v>366.2253188748173</v>
@@ -7356,19 +7356,19 @@
         <v>37.28</v>
       </c>
       <c r="U40" t="n">
-        <v>37.28</v>
+        <v>251.22105315343</v>
       </c>
       <c r="V40" t="n">
-        <v>37.28</v>
+        <v>422.322446039376</v>
       </c>
       <c r="W40" t="n">
-        <v>37.28</v>
+        <v>566.4933642990534</v>
       </c>
       <c r="X40" t="n">
-        <v>37.28</v>
+        <v>689.804155323247</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.28</v>
+        <v>773.4934560022792</v>
       </c>
     </row>
     <row r="41">
@@ -7402,10 +7402,10 @@
         <v>37.28</v>
       </c>
       <c r="J41" t="n">
-        <v>123.1780950233907</v>
+        <v>498.62</v>
       </c>
       <c r="K41" t="n">
-        <v>567.4404156955106</v>
+        <v>679.3541562311558</v>
       </c>
       <c r="L41" t="n">
         <v>1028.780415695511</v>
@@ -7414,13 +7414,13 @@
         <v>1028.780415695511</v>
       </c>
       <c r="N41" t="n">
-        <v>1490.12041569551</v>
+        <v>1028.780415695511</v>
       </c>
       <c r="O41" t="n">
-        <v>1659.96790486741</v>
+        <v>1198.62790486741</v>
       </c>
       <c r="P41" t="n">
-        <v>1864</v>
+        <v>1402.66</v>
       </c>
       <c r="Q41" t="n">
         <v>1864</v>
@@ -7429,25 +7429,25 @@
         <v>1864</v>
       </c>
       <c r="S41" t="n">
-        <v>1864</v>
+        <v>1720.420103585289</v>
       </c>
       <c r="T41" t="n">
-        <v>1864</v>
+        <v>1457.396770942356</v>
       </c>
       <c r="U41" t="n">
-        <v>1531.56920961792</v>
+        <v>1124.965980560276</v>
       </c>
       <c r="V41" t="n">
-        <v>1218.588377126179</v>
+        <v>811.985148068535</v>
       </c>
       <c r="W41" t="n">
-        <v>896.9990074484542</v>
+        <v>751.1182074642131</v>
       </c>
       <c r="X41" t="n">
-        <v>621.9668524376787</v>
+        <v>751.1182074642131</v>
       </c>
       <c r="Y41" t="n">
-        <v>621.9668524376787</v>
+        <v>751.1182074642131</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>606.4088083995409</v>
+        <v>853.8237683805701</v>
       </c>
       <c r="C42" t="n">
-        <v>564.8937453232588</v>
+        <v>812.308705304288</v>
       </c>
       <c r="D42" t="n">
-        <v>213.4415363356804</v>
+        <v>784.0888195490328</v>
       </c>
       <c r="E42" t="n">
-        <v>190.5404280307181</v>
+        <v>437.9553880117473</v>
       </c>
       <c r="F42" t="n">
-        <v>170.7058398106405</v>
+        <v>418.1207997916696</v>
       </c>
       <c r="G42" t="n">
-        <v>165.6839720504642</v>
+        <v>89.86660879917008</v>
       </c>
       <c r="H42" t="n">
         <v>37.28</v>
@@ -7481,19 +7481,19 @@
         <v>37.28</v>
       </c>
       <c r="J42" t="n">
-        <v>37.28</v>
+        <v>233.0594978168084</v>
       </c>
       <c r="K42" t="n">
-        <v>349.2297246792891</v>
+        <v>545.0092224960974</v>
       </c>
       <c r="L42" t="n">
-        <v>785.6419990103384</v>
+        <v>855.3913332014703</v>
       </c>
       <c r="M42" t="n">
-        <v>1064.341890753198</v>
+        <v>855.3913332014703</v>
       </c>
       <c r="N42" t="n">
-        <v>1395.339586398502</v>
+        <v>1186.389028846774</v>
       </c>
       <c r="O42" t="n">
         <v>1606.304284398418</v>
@@ -7502,31 +7502,31 @@
         <v>1864</v>
       </c>
       <c r="Q42" t="n">
-        <v>1864</v>
+        <v>1788.182636748706</v>
       </c>
       <c r="R42" t="n">
-        <v>1682.588426596225</v>
+        <v>1606.77106334493</v>
       </c>
       <c r="S42" t="n">
-        <v>1548.951214891929</v>
+        <v>1473.133851640634</v>
       </c>
       <c r="T42" t="n">
-        <v>1465.857636532328</v>
+        <v>1390.040273281034</v>
       </c>
       <c r="U42" t="n">
-        <v>1061.655777045195</v>
+        <v>1309.070737026224</v>
       </c>
       <c r="V42" t="n">
-        <v>966.1904566497199</v>
+        <v>1213.605416630749</v>
       </c>
       <c r="W42" t="n">
-        <v>852.6822314882769</v>
+        <v>1100.097191469306</v>
       </c>
       <c r="X42" t="n">
-        <v>751.8107775030369</v>
+        <v>999.225737484066</v>
       </c>
       <c r="Y42" t="n">
-        <v>671.6174514766385</v>
+        <v>919.0324114576676</v>
       </c>
     </row>
     <row r="43">
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>665.1745250991181</v>
+        <v>664.0499031273587</v>
       </c>
       <c r="C43" t="n">
-        <v>711.9765309175539</v>
+        <v>710.8519089457944</v>
       </c>
       <c r="D43" t="n">
-        <v>746.0956750425539</v>
+        <v>744.9710530707945</v>
       </c>
       <c r="E43" t="n">
-        <v>784.7245792539669</v>
+        <v>783.5999572822075</v>
       </c>
       <c r="F43" t="n">
-        <v>829.8855518459025</v>
+        <v>828.760929874143</v>
       </c>
       <c r="G43" t="n">
-        <v>904.7294505196729</v>
+        <v>903.6048285479135</v>
       </c>
       <c r="H43" t="n">
         <v>999.5878815761635</v>
@@ -7590,22 +7590,22 @@
         <v>37.28</v>
       </c>
       <c r="T43" t="n">
-        <v>148.8788283391327</v>
+        <v>147.7542063673733</v>
       </c>
       <c r="U43" t="n">
-        <v>316.2647845839767</v>
+        <v>315.1401626122174</v>
       </c>
       <c r="V43" t="n">
-        <v>435.8861774699227</v>
+        <v>434.7615554981633</v>
       </c>
       <c r="W43" t="n">
-        <v>528.5770957296002</v>
+        <v>527.4524737578407</v>
       </c>
       <c r="X43" t="n">
-        <v>600.4078867537937</v>
+        <v>599.2832647820343</v>
       </c>
       <c r="Y43" t="n">
-        <v>632.617187432826</v>
+        <v>631.4925654610665</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>37.28</v>
+        <v>282.2947293369026</v>
       </c>
       <c r="C44" t="n">
-        <v>37.28</v>
+        <v>282.2947293369026</v>
       </c>
       <c r="D44" t="n">
-        <v>37.28</v>
+        <v>282.2947293369026</v>
       </c>
       <c r="E44" t="n">
-        <v>37.28</v>
+        <v>197.0792852895605</v>
       </c>
       <c r="F44" t="n">
-        <v>37.28</v>
+        <v>111.332185584498</v>
       </c>
       <c r="G44" t="n">
-        <v>37.28</v>
+        <v>111.332185584498</v>
       </c>
       <c r="H44" t="n">
         <v>37.28</v>
@@ -7645,19 +7645,19 @@
         <v>584.5180950233907</v>
       </c>
       <c r="L44" t="n">
-        <v>808.734797435451</v>
+        <v>1028.780415695511</v>
       </c>
       <c r="M44" t="n">
-        <v>1270.074797435451</v>
+        <v>1490.12041569551</v>
       </c>
       <c r="N44" t="n">
-        <v>1270.074797435451</v>
+        <v>1490.12041569551</v>
       </c>
       <c r="O44" t="n">
-        <v>1439.922286607351</v>
+        <v>1659.96790486741</v>
       </c>
       <c r="P44" t="n">
-        <v>1643.954381739941</v>
+        <v>1864</v>
       </c>
       <c r="Q44" t="n">
         <v>1864</v>
@@ -7666,25 +7666,25 @@
         <v>1864</v>
       </c>
       <c r="S44" t="n">
-        <v>1720.420103585289</v>
+        <v>1864</v>
       </c>
       <c r="T44" t="n">
-        <v>1457.396770942356</v>
+        <v>1864</v>
       </c>
       <c r="U44" t="n">
-        <v>1124.965980560276</v>
+        <v>1531.56920961792</v>
       </c>
       <c r="V44" t="n">
-        <v>811.985148068535</v>
+        <v>1218.588377126179</v>
       </c>
       <c r="W44" t="n">
-        <v>490.3957783908102</v>
+        <v>896.9990074484542</v>
       </c>
       <c r="X44" t="n">
-        <v>215.3636233800347</v>
+        <v>621.9668524376787</v>
       </c>
       <c r="Y44" t="n">
-        <v>37.28</v>
+        <v>428.7169204348439</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>283.1764851672179</v>
+        <v>283.1764851672177</v>
       </c>
       <c r="C45" t="n">
-        <v>241.6614220909358</v>
+        <v>241.6614220909356</v>
       </c>
       <c r="D45" t="n">
-        <v>213.4415363356806</v>
+        <v>213.4415363356804</v>
       </c>
       <c r="E45" t="n">
-        <v>190.5404280307184</v>
+        <v>190.5404280307182</v>
       </c>
       <c r="F45" t="n">
-        <v>170.7058398106407</v>
+        <v>170.7058398106406</v>
       </c>
       <c r="G45" t="n">
-        <v>165.6839720504644</v>
+        <v>165.6839720504643</v>
       </c>
       <c r="H45" t="n">
         <v>37.28</v>
@@ -7718,16 +7718,16 @@
         <v>37.28</v>
       </c>
       <c r="J45" t="n">
-        <v>37.28</v>
+        <v>233.0594978168084</v>
       </c>
       <c r="K45" t="n">
-        <v>349.2297246792891</v>
+        <v>545.0092224960974</v>
       </c>
       <c r="L45" t="n">
-        <v>785.6419990103384</v>
+        <v>981.4214968271467</v>
       </c>
       <c r="M45" t="n">
-        <v>1064.341890753198</v>
+        <v>981.4214968271467</v>
       </c>
       <c r="N45" t="n">
         <v>1186.389028846774</v>
@@ -7751,19 +7751,19 @@
         <v>1465.857636532328</v>
       </c>
       <c r="U45" t="n">
-        <v>1384.888100277518</v>
+        <v>1061.655777045195</v>
       </c>
       <c r="V45" t="n">
-        <v>1289.422779882043</v>
+        <v>642.9581334173965</v>
       </c>
       <c r="W45" t="n">
-        <v>852.682231488277</v>
+        <v>529.4499082559536</v>
       </c>
       <c r="X45" t="n">
-        <v>428.5784542707138</v>
+        <v>428.5784542707136</v>
       </c>
       <c r="Y45" t="n">
-        <v>348.3851282443155</v>
+        <v>348.3851282443153</v>
       </c>
     </row>
     <row r="46">
@@ -7967,25 +7967,25 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L2" t="n">
-        <v>183.3412755627362</v>
+        <v>309.2909949748743</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>704.292876848652</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>294.1798838637633</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
         <v>404.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>375.1590153027356</v>
+        <v>184.5002908654719</v>
       </c>
       <c r="P5" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
         <v>321.8400703517588</v>
       </c>
       <c r="L8" t="n">
-        <v>294.1798838637633</v>
+        <v>235.5012052109776</v>
       </c>
       <c r="M8" t="n">
         <v>472.2608914614128</v>
@@ -8456,7 +8456,7 @@
         <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>128.5418702571336</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>469.4402462311558</v>
       </c>
       <c r="L11" t="n">
-        <v>425.5184824120603</v>
+        <v>425.5184824120604</v>
       </c>
       <c r="M11" t="n">
-        <v>944.2578010091515</v>
+        <v>292.2578010091515</v>
       </c>
       <c r="N11" t="n">
-        <v>382.4016053149082</v>
+        <v>604.0968687287514</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,16 +8912,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>469.4402462311558</v>
+        <v>238.7557007748663</v>
       </c>
       <c r="L14" t="n">
-        <v>156.4484131714792</v>
+        <v>425.5184824120603</v>
       </c>
       <c r="M14" t="n">
-        <v>944.2578010091515</v>
+        <v>292.2578010091515</v>
       </c>
       <c r="N14" t="n">
         <v>221.1669379693327</v>
@@ -8930,10 +8930,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>445.9069746135458</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.83983508125425</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9626,10 +9626,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>404.1933959887916</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>944.2578010091515</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>469.4402462311558</v>
       </c>
       <c r="L26" t="n">
-        <v>233.9694466007697</v>
+        <v>210.4361749831598</v>
       </c>
       <c r="M26" t="n">
         <v>292.2578010091515</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>445.9069746135458</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>458.1811578004721</v>
+        <v>27.87642121431531</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10346,7 +10346,7 @@
         <v>944.2578010091515</v>
       </c>
       <c r="N32" t="n">
-        <v>221.1669379693327</v>
+        <v>382.4016053149082</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>179.0745024268297</v>
+        <v>17.83983508125425</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,22 +10574,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>283.4402462311558</v>
+        <v>266.190065091883</v>
       </c>
       <c r="L35" t="n">
         <v>239.5184824120603</v>
       </c>
       <c r="M35" t="n">
-        <v>292.2578010091515</v>
+        <v>758.2578010091515</v>
       </c>
       <c r="N35" t="n">
-        <v>410.0097822165142</v>
+        <v>221.1669379693327</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>259.9069746135457</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>17.83983508125425</v>
@@ -10650,7 +10650,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>227.4647419277884</v>
+        <v>206.735840641591</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
@@ -10665,7 +10665,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>361.9528975147064</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>379.2342474511205</v>
       </c>
       <c r="K38" t="n">
-        <v>283.4402462311558</v>
+        <v>126.4743000528227</v>
       </c>
       <c r="L38" t="n">
-        <v>222.2683012727874</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>292.2578010091515</v>
@@ -10887,13 +10887,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>29.70767342596176</v>
+        <v>201.3283029826966</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>177.0281672156291</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,7 +10902,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>382.6817988009037</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>219.1507118405495</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>379.2342474511205</v>
       </c>
       <c r="K41" t="n">
-        <v>266.190065091883</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>239.5184824120603</v>
+        <v>126.4743000528227</v>
       </c>
       <c r="M41" t="n">
         <v>292.2578010091515</v>
       </c>
       <c r="N41" t="n">
-        <v>687.1669379693327</v>
+        <v>221.1669379693327</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>17.83983508125425</v>
+        <v>483.8398350812543</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,22 +11124,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>29.70767342596176</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>388.0893364597981</v>
+        <v>260.7861408783069</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>190.1797782656032</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>171.6206295567345</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11288,7 +11288,7 @@
         <v>283.4402462311558</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>222.2683012727874</v>
       </c>
       <c r="M44" t="n">
         <v>758.2578010091515</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>240.1081363540416</v>
+        <v>17.83983508125425</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,7 +11361,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>29.70767342596176</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
@@ -11370,10 +11370,10 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M45" t="n">
-        <v>471.6948204301074</v>
+        <v>190.1797782656032</v>
       </c>
       <c r="N45" t="n">
-        <v>274.3473579271811</v>
+        <v>358.1053315898589</v>
       </c>
       <c r="O45" t="n">
         <v>382.6817988009037</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>4.791722574282176e-13</v>
+        <v>1.032954436203123e-12</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>127.8598414762692</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25644,10 +25644,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>142.1440974505641</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>260.3930993165036</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -25656,10 +25656,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>258.1152047826689</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>272.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>191.3174326828064</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>161.9993129555745</v>
+        <v>17.04134376861259</v>
       </c>
       <c r="C44" t="n">
         <v>129.4745782429939</v>
@@ -25839,16 +25839,16 @@
         <v>90.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>84.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>84.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>82.32219640761923</v>
       </c>
       <c r="H44" t="n">
-        <v>73.31166372865306</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,10 +25881,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>142.1440974505641</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>260.3930993165036</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>15.01464553657209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -26272,7 +26272,7 @@
         <v>1227892.61432428</v>
       </c>
       <c r="C2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324279</v>
       </c>
       <c r="D2" t="n">
         <v>1227892.61432428</v>
@@ -26299,13 +26299,13 @@
         <v>1227892.61432428</v>
       </c>
       <c r="L2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324281</v>
       </c>
       <c r="M2" t="n">
         <v>1227892.61432428</v>
       </c>
       <c r="N2" t="n">
-        <v>1227892.614324281</v>
+        <v>1227892.61432428</v>
       </c>
       <c r="O2" t="n">
         <v>1171880.354235702</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.2919515911</v>
       </c>
       <c r="E4" t="n">
-        <v>511269.9826128767</v>
+        <v>511074.1690089637</v>
       </c>
       <c r="F4" t="n">
-        <v>509593.2914637273</v>
+        <v>509397.4778598144</v>
       </c>
       <c r="G4" t="n">
-        <v>507914.2865436997</v>
+        <v>507718.4729397869</v>
       </c>
       <c r="H4" t="n">
-        <v>506232.9512606539</v>
+        <v>506037.1376567408</v>
       </c>
       <c r="I4" t="n">
-        <v>504549.2688062633</v>
+        <v>504353.4552023503</v>
       </c>
       <c r="J4" t="n">
-        <v>502863.2221519142</v>
+        <v>502667.4085480013</v>
       </c>
       <c r="K4" t="n">
-        <v>501174.7940445096</v>
+        <v>500978.9804405967</v>
       </c>
       <c r="L4" t="n">
-        <v>499483.9670021611</v>
+        <v>499288.1533982481</v>
       </c>
       <c r="M4" t="n">
-        <v>514822.4743070321</v>
+        <v>514672.9534802454</v>
       </c>
       <c r="N4" t="n">
-        <v>512953.4824301332</v>
+        <v>512803.9616033464</v>
       </c>
       <c r="O4" t="n">
-        <v>480003.8779493121</v>
+        <v>479854.3571225255</v>
       </c>
       <c r="P4" t="n">
-        <v>478263.4973813285</v>
+        <v>478113.9765545417</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>335785.0381141612</v>
+        <v>335984.3527693759</v>
       </c>
       <c r="C6" t="n">
-        <v>568891.9603016496</v>
+        <v>569091.2749568642</v>
       </c>
       <c r="D6" t="n">
-        <v>570903.6077174739</v>
+        <v>571102.9223726887</v>
       </c>
       <c r="E6" t="n">
-        <v>39815.35171140337</v>
+        <v>40011.16531531615</v>
       </c>
       <c r="F6" t="n">
-        <v>643973.0428605524</v>
+        <v>644168.8564644656</v>
       </c>
       <c r="G6" t="n">
-        <v>645652.0477805806</v>
+        <v>645847.8613844932</v>
       </c>
       <c r="H6" t="n">
-        <v>647333.3830636261</v>
+        <v>647529.1966675392</v>
       </c>
       <c r="I6" t="n">
-        <v>649017.0655180169</v>
+        <v>649212.8791219294</v>
       </c>
       <c r="J6" t="n">
-        <v>263055.1121723661</v>
+        <v>263250.9257762785</v>
       </c>
       <c r="K6" t="n">
-        <v>652391.5402797706</v>
+        <v>652587.3538836833</v>
       </c>
       <c r="L6" t="n">
-        <v>654082.3673221187</v>
+        <v>654278.1809260326</v>
       </c>
       <c r="M6" t="n">
-        <v>571697.072017248</v>
+        <v>571846.5928440345</v>
       </c>
       <c r="N6" t="n">
-        <v>647550.0638941476</v>
+        <v>647699.5847209337</v>
       </c>
       <c r="O6" t="n">
-        <v>414458.9962863901</v>
+        <v>414608.5171131768</v>
       </c>
       <c r="P6" t="n">
-        <v>630599.3768543733</v>
+        <v>630748.89768116</v>
       </c>
     </row>
   </sheetData>
@@ -26993,22 +26993,22 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>320</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>52</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>268</v>
@@ -27106,7 +27106,7 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>92</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649895</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321728</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,28 +27512,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>71.08419617656375</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>107.4561141864639</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>30.47344446279683</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27594,22 +27594,22 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>352.3771867701062</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>235.7137041103819</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
         <v>171.1020457840527</v>
@@ -27618,7 +27618,7 @@
         <v>396.2647849014816</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
         <v>396.2015953708939</v>
@@ -27648,16 +27648,16 @@
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,22 +27749,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.68558767074182</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>330.0491815260438</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>371.6127482155553</v>
       </c>
     </row>
     <row r="7">
@@ -27840,7 +27840,7 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>244.8599384153005</v>
@@ -27849,7 +27849,7 @@
         <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>391.4355340580694</v>
       </c>
       <c r="J7" t="n">
         <v>396.2647849014816</v>
@@ -27858,7 +27858,7 @@
         <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27882,13 +27882,13 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
         <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>307.7534137377781</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I8" t="n">
         <v>134.2726973711268</v>
@@ -27958,7 +27958,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -27995,19 +27995,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>157.1970077340414</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>131.0292198606515</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28068,7 +28068,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28083,16 +28083,16 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>295.4264488046217</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>347.6775194675575</v>
       </c>
       <c r="L10" t="n">
         <v>396.2015953708939</v>
@@ -28119,7 +28119,7 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
         <v>150.9483584875727</v>
@@ -28131,10 +28131,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>320</v>
       </c>
       <c r="I11" t="n">
-        <v>94.75154159223234</v>
+        <v>94.63721251837561</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>160.7262319941236</v>
       </c>
       <c r="S11" t="n">
-        <v>319.8856709261432</v>
+        <v>320</v>
       </c>
       <c r="T11" t="n">
         <v>320</v>
@@ -28226,13 +28226,13 @@
         <v>320</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D12" t="n">
-        <v>320</v>
+        <v>116.9492302302902</v>
       </c>
       <c r="E12" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>320</v>
@@ -28271,7 +28271,7 @@
         <v>75.05918961878146</v>
       </c>
       <c r="R12" t="n">
-        <v>116.94923023029</v>
+        <v>320</v>
       </c>
       <c r="S12" t="n">
         <v>320</v>
@@ -28280,7 +28280,7 @@
         <v>320</v>
       </c>
       <c r="U12" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -28292,7 +28292,7 @@
         <v>320</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13">
@@ -28320,7 +28320,7 @@
         <v>320</v>
       </c>
       <c r="H13" t="n">
-        <v>318.8640182103437</v>
+        <v>320</v>
       </c>
       <c r="I13" t="n">
         <v>320</v>
@@ -28329,7 +28329,7 @@
         <v>320</v>
       </c>
       <c r="K13" t="n">
-        <v>320</v>
+        <v>318.8640182103439</v>
       </c>
       <c r="L13" t="n">
         <v>320</v>
@@ -28402,7 +28402,7 @@
         <v>320</v>
       </c>
       <c r="I14" t="n">
-        <v>94.63721251837561</v>
+        <v>94.75154159223234</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>160.7262319941236</v>
+        <v>160.6119029202667</v>
       </c>
       <c r="S14" t="n">
         <v>320</v>
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>116.94923023029</v>
       </c>
       <c r="C15" t="n">
         <v>320</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="F15" t="n">
-        <v>116.9492302302899</v>
+        <v>320</v>
       </c>
       <c r="G15" t="n">
         <v>320</v>
@@ -28523,13 +28523,13 @@
         <v>320</v>
       </c>
       <c r="W15" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28596,13 +28596,13 @@
         <v>320</v>
       </c>
       <c r="U16" t="n">
+        <v>320</v>
+      </c>
+      <c r="V16" t="n">
+        <v>320</v>
+      </c>
+      <c r="W16" t="n">
         <v>318.8640182103437</v>
-      </c>
-      <c r="V16" t="n">
-        <v>320</v>
-      </c>
-      <c r="W16" t="n">
-        <v>320</v>
       </c>
       <c r="X16" t="n">
         <v>320</v>
@@ -28639,7 +28639,7 @@
         <v>320</v>
       </c>
       <c r="I17" t="n">
-        <v>94.63721251837558</v>
+        <v>94.75154159223234</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28675,7 +28675,7 @@
         <v>320</v>
       </c>
       <c r="U17" t="n">
-        <v>320</v>
+        <v>319.8856709261431</v>
       </c>
       <c r="V17" t="n">
         <v>320</v>
@@ -28697,19 +28697,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>116.9492302302898</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>320</v>
+        <v>192.0084198490714</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G18" t="n">
         <v>320</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>320</v>
@@ -28763,10 +28763,10 @@
         <v>320</v>
       </c>
       <c r="X18" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28776,7 +28776,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>320</v>
+        <v>318.8640182103437</v>
       </c>
       <c r="C19" t="n">
         <v>320</v>
@@ -28845,7 +28845,7 @@
         <v>320</v>
       </c>
       <c r="Y19" t="n">
-        <v>318.8640182103437</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20">
@@ -28934,16 +28934,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>116.94923023029</v>
       </c>
       <c r="C21" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>320</v>
@@ -28991,13 +28991,13 @@
         <v>320</v>
       </c>
       <c r="U21" t="n">
-        <v>116.9492302302901</v>
+        <v>320</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="X21" t="n">
         <v>320</v>
@@ -29028,49 +29028,49 @@
         <v>320</v>
       </c>
       <c r="G22" t="n">
+        <v>320</v>
+      </c>
+      <c r="H22" t="n">
+        <v>320</v>
+      </c>
+      <c r="I22" t="n">
+        <v>320</v>
+      </c>
+      <c r="J22" t="n">
+        <v>320</v>
+      </c>
+      <c r="K22" t="n">
+        <v>320</v>
+      </c>
+      <c r="L22" t="n">
+        <v>320</v>
+      </c>
+      <c r="M22" t="n">
+        <v>320</v>
+      </c>
+      <c r="N22" t="n">
+        <v>320</v>
+      </c>
+      <c r="O22" t="n">
+        <v>320</v>
+      </c>
+      <c r="P22" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>320</v>
+      </c>
+      <c r="R22" t="n">
+        <v>320</v>
+      </c>
+      <c r="S22" t="n">
+        <v>320</v>
+      </c>
+      <c r="T22" t="n">
+        <v>320</v>
+      </c>
+      <c r="U22" t="n">
         <v>318.8640182103437</v>
-      </c>
-      <c r="H22" t="n">
-        <v>320</v>
-      </c>
-      <c r="I22" t="n">
-        <v>320</v>
-      </c>
-      <c r="J22" t="n">
-        <v>320</v>
-      </c>
-      <c r="K22" t="n">
-        <v>320</v>
-      </c>
-      <c r="L22" t="n">
-        <v>320</v>
-      </c>
-      <c r="M22" t="n">
-        <v>320</v>
-      </c>
-      <c r="N22" t="n">
-        <v>320</v>
-      </c>
-      <c r="O22" t="n">
-        <v>320</v>
-      </c>
-      <c r="P22" t="n">
-        <v>320</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>320</v>
-      </c>
-      <c r="R22" t="n">
-        <v>320</v>
-      </c>
-      <c r="S22" t="n">
-        <v>320</v>
-      </c>
-      <c r="T22" t="n">
-        <v>320</v>
-      </c>
-      <c r="U22" t="n">
-        <v>320</v>
       </c>
       <c r="V22" t="n">
         <v>320</v>
@@ -29110,10 +29110,10 @@
         <v>320</v>
       </c>
       <c r="H23" t="n">
-        <v>319.8856709261432</v>
+        <v>320</v>
       </c>
       <c r="I23" t="n">
-        <v>94.75154159223234</v>
+        <v>94.63721251837561</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29171,11 +29171,11 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>320</v>
+      </c>
+      <c r="C24" t="n">
         <v>116.94923023029</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
@@ -29183,7 +29183,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>320</v>
@@ -29253,7 +29253,7 @@
         <v>320</v>
       </c>
       <c r="C25" t="n">
-        <v>318.8640182103437</v>
+        <v>320</v>
       </c>
       <c r="D25" t="n">
         <v>320</v>
@@ -29271,7 +29271,7 @@
         <v>320</v>
       </c>
       <c r="I25" t="n">
-        <v>320</v>
+        <v>318.8640182103438</v>
       </c>
       <c r="J25" t="n">
         <v>320</v>
@@ -29347,7 +29347,7 @@
         <v>320</v>
       </c>
       <c r="H26" t="n">
-        <v>319.8856709261432</v>
+        <v>320</v>
       </c>
       <c r="I26" t="n">
         <v>94.75154159223234</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>160.7262319941236</v>
+        <v>160.6119029202667</v>
       </c>
       <c r="S26" t="n">
         <v>320</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>320</v>
@@ -29417,16 +29417,16 @@
         <v>320</v>
       </c>
       <c r="E27" t="n">
-        <v>320</v>
+        <v>192.0084198490713</v>
       </c>
       <c r="F27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="I27" t="n">
         <v>190.6881783441787</v>
@@ -29453,10 +29453,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="S27" t="n">
         <v>320</v>
@@ -29468,7 +29468,7 @@
         <v>320</v>
       </c>
       <c r="V27" t="n">
-        <v>116.94923023029</v>
+        <v>320</v>
       </c>
       <c r="W27" t="n">
         <v>320</v>
@@ -29477,7 +29477,7 @@
         <v>320</v>
       </c>
       <c r="Y27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29505,13 +29505,13 @@
         <v>320</v>
       </c>
       <c r="H28" t="n">
-        <v>320</v>
+        <v>318.8640182103437</v>
       </c>
       <c r="I28" t="n">
         <v>320</v>
       </c>
       <c r="J28" t="n">
-        <v>318.8640182103438</v>
+        <v>320</v>
       </c>
       <c r="K28" t="n">
         <v>320</v>
@@ -29584,7 +29584,7 @@
         <v>320</v>
       </c>
       <c r="H29" t="n">
-        <v>320</v>
+        <v>319.8856709261432</v>
       </c>
       <c r="I29" t="n">
         <v>94.75154159223234</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>160.6119029202667</v>
+        <v>160.7262319941236</v>
       </c>
       <c r="S29" t="n">
         <v>320</v>
@@ -29651,22 +29651,22 @@
         <v>320</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E30" t="n">
-        <v>307.6374085744685</v>
+        <v>320</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G30" t="n">
         <v>320</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>190.6881783441787</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29693,7 +29693,7 @@
         <v>75.05918961878146</v>
       </c>
       <c r="R30" t="n">
-        <v>320</v>
+        <v>116.94923023029</v>
       </c>
       <c r="S30" t="n">
         <v>320</v>
@@ -29705,13 +29705,13 @@
         <v>320</v>
       </c>
       <c r="V30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>320</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>116.94923023029</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>116.9492302302901</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E33" t="n">
         <v>320</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G33" t="n">
         <v>320</v>
@@ -29942,10 +29942,10 @@
         <v>320</v>
       </c>
       <c r="V33" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>320</v>
@@ -30061,7 +30061,7 @@
         <v>372</v>
       </c>
       <c r="I35" t="n">
-        <v>88.46601251837583</v>
+        <v>94.75154159223234</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>160.7262319941236</v>
+        <v>154.4407029202671</v>
       </c>
       <c r="S35" t="n">
         <v>372</v>
@@ -30119,16 +30119,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30170,7 +30170,7 @@
         <v>372</v>
       </c>
       <c r="S36" t="n">
-        <v>372</v>
+        <v>72.27217624958934</v>
       </c>
       <c r="T36" t="n">
         <v>372</v>
@@ -30182,13 +30182,13 @@
         <v>372</v>
       </c>
       <c r="W36" t="n">
-        <v>125.6623921299741</v>
+        <v>372</v>
       </c>
       <c r="X36" t="n">
         <v>372</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37">
@@ -30204,10 +30204,10 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D37" t="n">
-        <v>372</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E37" t="n">
-        <v>372</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
         <v>274.3828559677419</v>
@@ -30222,13 +30222,13 @@
         <v>372</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="K37" t="n">
         <v>372</v>
       </c>
       <c r="L37" t="n">
-        <v>337.008044666579</v>
+        <v>372</v>
       </c>
       <c r="M37" t="n">
         <v>372</v>
@@ -30249,19 +30249,19 @@
         <v>372</v>
       </c>
       <c r="S37" t="n">
-        <v>351.1543157684292</v>
+        <v>372</v>
       </c>
       <c r="T37" t="n">
-        <v>207.2739107685528</v>
+        <v>323.6230619519796</v>
       </c>
       <c r="U37" t="n">
-        <v>372</v>
+        <v>150.9232765203596</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>372</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
@@ -30298,7 +30298,7 @@
         <v>372</v>
       </c>
       <c r="I38" t="n">
-        <v>88.46601251837583</v>
+        <v>94.75154159223234</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>160.7262319941236</v>
+        <v>154.4407029202671</v>
       </c>
       <c r="S38" t="n">
         <v>372</v>
@@ -30356,19 +30356,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>294.8869003665102</v>
       </c>
       <c r="C39" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>112.5001665821573</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>324.9716490825745</v>
@@ -30377,7 +30377,7 @@
         <v>324.7519173751004</v>
       </c>
       <c r="I39" t="n">
-        <v>190.6881783441787</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30410,10 +30410,10 @@
         <v>372</v>
       </c>
       <c r="T39" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>372</v>
@@ -30422,10 +30422,10 @@
         <v>372</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
     </row>
     <row r="40">
@@ -30435,10 +30435,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>287.1138003370787</v>
+        <v>372</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>372</v>
       </c>
       <c r="D40" t="n">
         <v>372</v>
@@ -30447,25 +30447,25 @@
         <v>372</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>372</v>
       </c>
       <c r="G40" t="n">
-        <v>372</v>
+        <v>244.4001023497268</v>
       </c>
       <c r="H40" t="n">
-        <v>372</v>
+        <v>223.0474211835858</v>
       </c>
       <c r="I40" t="n">
-        <v>372</v>
+        <v>157.2735211938888</v>
       </c>
       <c r="J40" t="n">
-        <v>331.711958307509</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>372</v>
+        <v>213.7263475716348</v>
       </c>
       <c r="L40" t="n">
-        <v>372</v>
+        <v>327.8365134036808</v>
       </c>
       <c r="M40" t="n">
         <v>372</v>
@@ -30492,19 +30492,19 @@
         <v>207.2739107685528</v>
       </c>
       <c r="U40" t="n">
-        <v>150.9232765203596</v>
+        <v>367.0253504127131</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>372</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>372</v>
       </c>
       <c r="X40" t="n">
-        <v>247.4436454301076</v>
+        <v>372</v>
       </c>
       <c r="Y40" t="n">
-        <v>287.4653528494624</v>
+        <v>372</v>
       </c>
     </row>
     <row r="41">
@@ -30599,19 +30599,19 @@
         <v>320</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E42" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>320</v>
       </c>
       <c r="G42" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>197.6319850451408</v>
+        <v>272.691174663922</v>
       </c>
       <c r="I42" t="n">
         <v>190.6881783441787</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>320</v>
@@ -30650,7 +30650,7 @@
         <v>320</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="V42" t="n">
         <v>320</v>
@@ -30690,7 +30690,7 @@
         <v>320</v>
       </c>
       <c r="H43" t="n">
-        <v>318.8640182103439</v>
+        <v>320</v>
       </c>
       <c r="I43" t="n">
         <v>320</v>
@@ -30726,7 +30726,7 @@
         <v>320</v>
       </c>
       <c r="T43" t="n">
-        <v>320</v>
+        <v>318.8640182103441</v>
       </c>
       <c r="U43" t="n">
         <v>320</v>
@@ -30848,7 +30848,7 @@
         <v>320</v>
       </c>
       <c r="H45" t="n">
-        <v>197.6319850451406</v>
+        <v>197.6319850451408</v>
       </c>
       <c r="I45" t="n">
         <v>190.6881783441787</v>
@@ -30887,16 +30887,16 @@
         <v>320</v>
       </c>
       <c r="U45" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="Y45" t="n">
         <v>320</v>
@@ -34746,25 +34746,25 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>248.0502805878618</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>300.2102102361032</v>
       </c>
       <c r="O2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,22 +34880,22 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>79.65194012206155</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>8.577922271058354</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34904,7 +34904,7 @@
         <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34934,16 +34934,16 @@
         <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
+        <v>52.15992964824119</v>
+      </c>
+      <c r="L5" t="n">
+        <v>64.70900502512563</v>
+      </c>
+      <c r="M5" t="n">
         <v>374</v>
       </c>
-      <c r="L5" t="n">
-        <v>358.888888888889</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>183.3412755627362</v>
+      </c>
+      <c r="P5" t="n">
+        <v>58.67867865278593</v>
+      </c>
+      <c r="Q5" t="n">
         <v>374</v>
-      </c>
-      <c r="P5" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35126,7 +35126,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -35135,7 +35135,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>220.3334882740167</v>
       </c>
       <c r="J7" t="n">
         <v>374</v>
@@ -35144,7 +35144,7 @@
         <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35168,13 +35168,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>108.5831035215619</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>358.888888888889</v>
+        <v>300.2102102361032</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35235,7 +35235,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>374</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35354,7 +35354,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35369,16 +35369,16 @@
         <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
-        <v>273.1616639031401</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>80.52658173198824</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -35417,10 +35417,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>86.76575254887953</v>
+        <v>517.0704891350363</v>
       </c>
       <c r="K11" t="n">
         <v>652</v>
@@ -35463,10 +35463,10 @@
         <v>652</v>
       </c>
       <c r="M11" t="n">
-        <v>652</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>161.2346673455755</v>
+        <v>382.9299307594187</v>
       </c>
       <c r="O11" t="n">
         <v>171.5631203756563</v>
@@ -35606,7 +35606,7 @@
         <v>75.59989765027325</v>
       </c>
       <c r="H13" t="n">
-        <v>95.81659702675789</v>
+        <v>96.95257881641416</v>
       </c>
       <c r="I13" t="n">
         <v>162.7264788061112</v>
@@ -35615,7 +35615,7 @@
         <v>330.245624934584</v>
       </c>
       <c r="K13" t="n">
-        <v>106.2736524283652</v>
+        <v>105.137670638709</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,16 +35691,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>517.0704891350363</v>
+        <v>86.76575254887953</v>
       </c>
       <c r="K14" t="n">
+        <v>421.3154545437105</v>
+      </c>
+      <c r="L14" t="n">
         <v>652</v>
       </c>
-      <c r="L14" t="n">
-        <v>382.9299307594188</v>
-      </c>
       <c r="M14" t="n">
-        <v>652</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -35709,10 +35709,10 @@
         <v>171.5631203756563</v>
       </c>
       <c r="P14" t="n">
-        <v>206.0930253864543</v>
+        <v>652</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>598.0122381883194</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35882,13 +35882,13 @@
         <v>112.7260892314472</v>
       </c>
       <c r="U16" t="n">
-        <v>167.9407416899841</v>
+        <v>169.0767234796404</v>
       </c>
       <c r="V16" t="n">
         <v>120.8296897837838</v>
       </c>
       <c r="W16" t="n">
-        <v>93.62719016129032</v>
+        <v>92.49120837163402</v>
       </c>
       <c r="X16" t="n">
         <v>72.55635456989245</v>
@@ -36062,7 +36062,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.88619966292134</v>
+        <v>31.75021787326501</v>
       </c>
       <c r="C19" t="n">
         <v>47.27475335195533</v>
@@ -36131,7 +36131,7 @@
         <v>72.55635456989245</v>
       </c>
       <c r="Y19" t="n">
-        <v>31.39866536088129</v>
+        <v>32.53464715053764</v>
       </c>
     </row>
     <row r="20">
@@ -36314,7 +36314,7 @@
         <v>45.61714403225807</v>
       </c>
       <c r="G22" t="n">
-        <v>74.46391586061698</v>
+        <v>75.59989765027325</v>
       </c>
       <c r="H22" t="n">
         <v>96.95257881641416</v>
@@ -36356,7 +36356,7 @@
         <v>112.7260892314472</v>
       </c>
       <c r="U22" t="n">
-        <v>169.0767234796404</v>
+        <v>167.9407416899841</v>
       </c>
       <c r="V22" t="n">
         <v>120.8296897837838</v>
@@ -36405,10 +36405,10 @@
         <v>86.76575254887953</v>
       </c>
       <c r="K23" t="n">
-        <v>586.7531497576358</v>
+        <v>182.5597537688442</v>
       </c>
       <c r="L23" t="n">
-        <v>226.4815175879397</v>
+        <v>630.6749135767313</v>
       </c>
       <c r="M23" t="n">
         <v>652</v>
@@ -36539,7 +36539,7 @@
         <v>32.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>46.13877156229897</v>
+        <v>47.27475335195533</v>
       </c>
       <c r="D25" t="n">
         <v>34.46378194444452</v>
@@ -36554,16 +36554,16 @@
         <v>75.59989765027325</v>
       </c>
       <c r="H25" t="n">
-        <v>96.95257881641417</v>
+        <v>96.95257881641416</v>
       </c>
       <c r="I25" t="n">
-        <v>162.7264788061112</v>
+        <v>161.590497016455</v>
       </c>
       <c r="J25" t="n">
         <v>330.245624934584</v>
       </c>
       <c r="K25" t="n">
-        <v>106.2736524283651</v>
+        <v>106.2736524283652</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36642,10 +36642,10 @@
         <v>517.0704891350363</v>
       </c>
       <c r="K26" t="n">
-        <v>182.5597537688442</v>
+        <v>652</v>
       </c>
       <c r="L26" t="n">
-        <v>460.4509641887095</v>
+        <v>436.9176925710995</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>171.5631203756563</v>
       </c>
       <c r="P26" t="n">
-        <v>652</v>
+        <v>206.0930253864543</v>
       </c>
       <c r="Q26" t="n">
         <v>598.0122381883194</v>
@@ -36791,16 +36791,16 @@
         <v>75.59989765027325</v>
       </c>
       <c r="H28" t="n">
-        <v>96.95257881641417</v>
+        <v>95.81659702675789</v>
       </c>
       <c r="I28" t="n">
         <v>162.7264788061112</v>
       </c>
       <c r="J28" t="n">
-        <v>329.1096431449278</v>
+        <v>330.245624934584</v>
       </c>
       <c r="K28" t="n">
-        <v>106.2736524283651</v>
+        <v>106.2736524283652</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>86.76575254887953</v>
+        <v>517.0704891350363</v>
       </c>
       <c r="K29" t="n">
-        <v>640.7409115693164</v>
+        <v>210.4361749831595</v>
       </c>
       <c r="L29" t="n">
         <v>226.4815175879397</v>
@@ -37125,7 +37125,7 @@
         <v>652</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>161.2346673455755</v>
       </c>
       <c r="O32" t="n">
         <v>171.5631203756563</v>
@@ -37134,7 +37134,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q32" t="n">
-        <v>161.2346673455755</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>75.59989765027325</v>
       </c>
       <c r="H34" t="n">
-        <v>96.95257881641416</v>
+        <v>96.95257881641417</v>
       </c>
       <c r="I34" t="n">
         <v>162.7264788061112</v>
@@ -37274,7 +37274,7 @@
         <v>330.245624934584</v>
       </c>
       <c r="K34" t="n">
-        <v>106.2736524283652</v>
+        <v>106.2736524283651</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37353,22 +37353,22 @@
         <v>86.76575254887953</v>
       </c>
       <c r="K35" t="n">
-        <v>466</v>
+        <v>448.7498188607271</v>
       </c>
       <c r="L35" t="n">
         <v>466</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="N35" t="n">
-        <v>188.8428442471815</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>171.5631203756563</v>
       </c>
       <c r="P35" t="n">
-        <v>466</v>
+        <v>206.0930253864543</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>197.7570685018267</v>
+        <v>177.0281672156292</v>
       </c>
       <c r="K36" t="n">
         <v>315.1007319992819</v>
@@ -37444,7 +37444,7 @@
         <v>334.3411067124284</v>
       </c>
       <c r="O36" t="n">
-        <v>403.4279225033414</v>
+        <v>424.1568237895389</v>
       </c>
       <c r="P36" t="n">
         <v>260.2987026278608</v>
@@ -37490,10 +37490,10 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>86.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>91.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -37508,13 +37508,13 @@
         <v>214.7264788061112</v>
       </c>
       <c r="J37" t="n">
-        <v>10.24562493458403</v>
+        <v>382.245624934584</v>
       </c>
       <c r="K37" t="n">
         <v>158.2736524283652</v>
       </c>
       <c r="L37" t="n">
-        <v>9.171531262898204</v>
+        <v>44.16348659631919</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,19 +37535,19 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>20.84568423157079</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>116.3491511834267</v>
       </c>
       <c r="U37" t="n">
-        <v>221.0767234796404</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>145.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -37587,13 +37587,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>86.76575254887953</v>
+        <v>466</v>
       </c>
       <c r="K38" t="n">
-        <v>466</v>
+        <v>309.0340538216669</v>
       </c>
       <c r="L38" t="n">
-        <v>448.7498188607271</v>
+        <v>226.4815175879397</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -37666,13 +37666,13 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>171.6206295567349</v>
       </c>
       <c r="K39" t="n">
         <v>315.1007319992819</v>
       </c>
       <c r="L39" t="n">
-        <v>229.759309878103</v>
+        <v>440.8204791222719</v>
       </c>
       <c r="M39" t="n">
         <v>281.5150421645043</v>
@@ -37681,7 +37681,7 @@
         <v>334.3411067124284</v>
       </c>
       <c r="O39" t="n">
-        <v>424.1568237895389</v>
+        <v>41.47502498863511</v>
       </c>
       <c r="P39" t="n">
         <v>260.2987026278608</v>
@@ -37721,10 +37721,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>84.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>99.27475335195533</v>
       </c>
       <c r="D40" t="n">
         <v>86.46378194444452</v>
@@ -37733,25 +37733,25 @@
         <v>91.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>97.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>127.5998976502732</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>148.9525788164142</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>214.7264788061112</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>341.9575832420931</v>
+        <v>10.24562493458403</v>
       </c>
       <c r="K40" t="n">
-        <v>158.2736524283652</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>44.16348659631922</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37778,19 +37778,19 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>216.1020738923535</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>172.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>145.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>124.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>84.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>86.76575254887953</v>
+        <v>466</v>
       </c>
       <c r="K41" t="n">
-        <v>448.7498188607271</v>
+        <v>182.5597537688442</v>
       </c>
       <c r="L41" t="n">
-        <v>466</v>
+        <v>352.9558176407625</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>466</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>171.5631203756563</v>
@@ -37845,7 +37845,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,22 +37903,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>197.7570685018267</v>
       </c>
       <c r="K42" t="n">
         <v>315.1007319992819</v>
       </c>
       <c r="L42" t="n">
-        <v>440.8204791222719</v>
+        <v>313.5172835407806</v>
       </c>
       <c r="M42" t="n">
-        <v>281.5150421645043</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>334.3411067124284</v>
       </c>
       <c r="O42" t="n">
-        <v>213.0956545453696</v>
+        <v>424.1568237895389</v>
       </c>
       <c r="P42" t="n">
         <v>260.2987026278608</v>
@@ -37976,7 +37976,7 @@
         <v>75.59989765027325</v>
       </c>
       <c r="H43" t="n">
-        <v>95.81659702675812</v>
+        <v>96.95257881641417</v>
       </c>
       <c r="I43" t="n">
         <v>162.7264788061112</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>112.7260892314472</v>
+        <v>111.5901074417912</v>
       </c>
       <c r="U43" t="n">
         <v>169.0767234796404</v>
@@ -38067,7 +38067,7 @@
         <v>466</v>
       </c>
       <c r="L44" t="n">
-        <v>226.4815175879397</v>
+        <v>448.7498188607271</v>
       </c>
       <c r="M44" t="n">
         <v>466</v>
@@ -38082,7 +38082,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q44" t="n">
-        <v>222.2683012727873</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>197.7570685018267</v>
       </c>
       <c r="K45" t="n">
         <v>315.1007319992819</v>
@@ -38149,10 +38149,10 @@
         <v>440.8204791222719</v>
       </c>
       <c r="M45" t="n">
-        <v>281.5150421645043</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>123.2799374682593</v>
+        <v>207.0379111309371</v>
       </c>
       <c r="O45" t="n">
         <v>424.1568237895389</v>
